--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -13,25 +13,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; Data Migration" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$7</definedName>
     <definedName name="Accuracy">Assumptions!$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$J$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD items to deliver'!$A$4:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD items to deliver'!$A$4:$M$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Assumptions'!$A$4:$C$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Assumptions'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; Data Migration'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Best practice (blue)'!$A$4:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Assumptions'!$A$4:$C$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assumptions'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +48,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0#"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +91,16 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="002E7D32"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00616161"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001565C0"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -206,31 +222,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,10 +254,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -276,6 +292,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -403,7 +425,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -716,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E33"/>
+  <dimension ref="B4:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -882,7 +904,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -897,7 +919,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -908,11 +930,11 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Points of the FRS v1.4 that no BRD asks for and the standard system offers (green): no cost</t>
+          <t>Points of the FRS v1.4 that no BRD asks for and the iNXT BrokerVerse OOTB platform offers (green): no cost</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -923,73 +945,127 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements found in the validation of the FRS v1.4 (Annex X.2, AA.4): in scope, for planning</t>
+          <t>BRD requirements not (fully) in the iNXT BrokerVerse OOTB platform (FRS Annex X.2, AA.4): in-scope delivery work, for planning</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Covered by the Integration and Data Migration scope (grey label in the FRS, Annex AA.5): no change request, no cost here</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Insurance-broking best practices in no BRD, not in the FRS and not in OOTB (blue, FRS Annex AA.6): recommendations, not commitments</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
         </is>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D27" s="14" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>Change request</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>In no BRD and not offered by the standard system (orange in the FRS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>Not in the BRD, offered by the standard system at no cost (green in the FRS)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="15" t="inlineStr">
         <is>
+          <t>Change request</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>In no BRD and not (or only partly) in the iNXT BrokerVerse OOTB platform (orange in the FRS); also when already available in BIBS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Offered by OOTB</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Not in the BRD; offered by the iNXT BrokerVerse OOTB platform (brokerverse-platform), no cost (green in the FRS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Integration / Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Interfaces and data migration: covered by those workstreams, not a change request (grey label)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Best practice</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>In no BRD, FRS or OOTB: recommendation with indicative effort, excluded from the CR total (blue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
           <t>BRD requirement</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>In scope; delivered without a change request (black in the FRS)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="17" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1003,6 +1079,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1015,7 +1093,83 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Complexity</t>
+        </is>
+      </c>
+      <c r="B1" s="37" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1025,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1409,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>BDOI FRS v1.1 / best practice / iorta TechNXT</t>
+          <t>BDOI FRS / best practice / iorta TechNXT</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -1287,7 +1441,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>What the standard system offers today</t>
+          <t>What the iNXT BrokerVerse OOTB platform offers (brokerverse-platform)</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1535,17 +1689,17 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>OB-UA-nn</t>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1553,29 +1707,37 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr"/>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Screen or function of the OOTB platform, or not found</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr"/>
+          <t>Already in BIBS?</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Already available for BDOI in the BIBS system; the effort is still the CR value</t>
+        </is>
+      </c>
       <c r="D34" s="14" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1586,10 +1748,14 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>BRD reference</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr"/>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>OB-UA-nn</t>
+        </is>
+      </c>
       <c r="D35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1600,7 +1766,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>What BDOI gets</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr"/>
@@ -1614,7 +1780,7 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>OOTB status</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr"/>
@@ -1628,14 +1794,10 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Cost (man-days)</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>No change request</t>
-        </is>
-      </c>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr"/>
       <c r="D38" s="14" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1646,25 +1808,21 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>Former change request number, BRD it extends</t>
-        </is>
-      </c>
+          <t>What BDOI gets</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr"/>
       <c r="D39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>OOTB status</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr"/>
@@ -1673,57 +1831,73 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr"/>
+          <t>Cost (man-days)</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>No change request</t>
+        </is>
+      </c>
       <c r="D41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>BRD reference</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr"/>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Former change request number, BRD it extends</t>
+        </is>
+      </c>
       <c r="D42" s="14" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr"/>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+        </is>
+      </c>
       <c r="D43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>What is delivered</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr"/>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Screen or function of the OOTB platform</t>
+        </is>
+      </c>
       <c r="D44" s="14" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1734,14 +1908,10 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>Analysis and design</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Man-days</t>
-        </is>
-      </c>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr"/>
       <c r="D45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1752,14 +1922,10 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Backend and frontend</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>Man-days</t>
-        </is>
-      </c>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
       <c r="D46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1770,14 +1936,10 @@
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>Testing and UAT support</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>Man-days</t>
-        </is>
-      </c>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr"/>
       <c r="D47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1788,14 +1950,10 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Total man-days</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Formula</t>
-        </is>
-      </c>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
       <c r="D48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1806,44 +1964,44 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>In scope</t>
-        </is>
-      </c>
+          <t>What is delivered</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr"/>
       <c r="D49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr"/>
+          <t>Analysis and design</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
       <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Backend and frontend</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Enter the day rate here</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -1851,19 +2009,365 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>Testing and UAT support</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>Total man-days</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>In scope</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>brokerverse-platform</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>Already in BIBS?</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Already available for BDOI in the BIBS system</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>IS-UA-nn / DM-UA-nn</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr"/>
+      <c r="D61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr"/>
+      <c r="D62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr"/>
+      <c r="D63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr"/>
+      <c r="D64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>No CR cost here</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>BP-UA-nn</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr"/>
+      <c r="D67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Philippine market (IC, Data Privacy Act, AMLA) where relevant</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr"/>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Not part of the CR total</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr"/>
+      <c r="D71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Enter the day rate here</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="inlineStr"/>
+      <c r="C73" s="12" t="inlineStr"/>
+      <c r="D73" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D52"/>
+  <autoFilter ref="A4:D73"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1884,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1952,7 +2456,7 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-007 Supervisory and record-ownership access</t>
+          <t>CR-UA-003 Break-glass administrators</t>
         </is>
       </c>
       <c r="B5" s="24">
@@ -1973,14 +2477,14 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Medium priority; High complexity</t>
+          <t>High priority; Medium complexity</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-011 Approval times, reminders and escalation</t>
+          <t>CR-UA-007 Supervisory and record-ownership access</t>
         </is>
       </c>
       <c r="B6" s="24">
@@ -2001,14 +2505,14 @@
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Medium priority; Medium complexity</t>
+          <t>Medium priority; High complexity</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-012 Monthly access review report to Information Security</t>
+          <t>CR-UA-008 No conflicting permissions inside a group profile</t>
         </is>
       </c>
       <c r="B7" s="24">
@@ -2029,14 +2533,14 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Low priority; Low complexity</t>
+          <t>Medium priority; Low complexity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-014 Temporary access with an end date</t>
+          <t>CR-UA-009 Export file names</t>
         </is>
       </c>
       <c r="B8" s="24">
@@ -2057,91 +2561,246 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Low priority; Medium complexity</t>
+          <t>Low priority; Low complexity</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>Total of the 4 change requests</t>
-        </is>
-      </c>
-      <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="28">
-        <f>IF(DayRate="","",SUM(E5:E8))</f>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CR-UA-011 Approval times, reminders and escalation</t>
+        </is>
+      </c>
+      <c r="B9" s="24">
+        <f>'CR Effort'!N9</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>'CR Effort'!O9</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>'CR Effort'!P9</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>'CR Effort'!U9</f>
         <v/>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Cost appears when the day rate is entered on the sheet Assumptions</t>
+          <t>Medium priority; Medium complexity</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Points beyond the BRD offered as standard (13)</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>0</v>
+          <t>CR-UA-013 E-mail copy of the request notices</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>'CR Effort'!N10</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>'CR Effort'!O10</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>'CR Effort'!P10</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>'CR Effort'!U10</f>
+        <v/>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>No change request, no cost (sheet Beyond the BRD - OOTB)</t>
+          <t>Medium priority; Low complexity</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements to deliver (3, in scope)</t>
+          <t>CR-UA-014 Temporary access with an end date</t>
         </is>
       </c>
       <c r="B11" s="24">
-        <f>SUM('BRD items to deliver'!I5:I7)</f>
-        <v/>
-      </c>
-      <c r="C11" s="24" t="inlineStr"/>
-      <c r="D11" s="24" t="inlineStr"/>
-      <c r="E11" s="25" t="inlineStr">
+        <f>'CR Effort'!N11</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>'CR Effort'!O11</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>'CR Effort'!P11</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>'CR Effort'!U11</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Low priority; Medium complexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>CR-UA-016 Emergency role edit</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>'CR Effort'!N12</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>'CR Effort'!O12</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>'CR Effort'!P12</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>'CR Effort'!U12</f>
+        <v/>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Medium priority; Medium complexity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Total of the 8 change requests</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>SUM(B5:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>SUM(C5:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>SUM(D5:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>IF(DayRate="","",SUM(E5:E12))</f>
+        <v/>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Cost appears when the day rate is entered on the sheet Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Points beyond the BRD offered by iNXT BrokerVerse OOTB (5)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>No change request, no cost (sheet Beyond the BRD - OOTB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirements to deliver (15, in scope)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>SUM('BRD items to deliver'!I5:I19)</f>
+        <v/>
+      </c>
+      <c r="C15" s="24" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Not charged</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>For planning only (FRS Annex AA.4)</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Integration and Data Migration scope (6)</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr"/>
+      <c r="C16" s="24" t="inlineStr"/>
+      <c r="D16" s="24" t="inlineStr"/>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Not here</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Covered by the Integration and Data Migration workstreams (FRS Annex AA.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Best-practice recommendations (6, blue)</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>SUM('Best practice (blue)'!E5:E10)</f>
+        <v/>
+      </c>
+      <c r="C17" s="24" t="inlineStr"/>
+      <c r="D17" s="24" t="inlineStr"/>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>Indicative</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Excluded from the CR total (FRS Annex AA.6)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F11"/>
+  <autoFilter ref="A4:F17"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F511">
+  <conditionalFormatting sqref="A5:F517">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2166,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2849,9 @@
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2228,6 +2890,9 @@
       <c r="S3" s="22" t="n"/>
       <c r="T3" s="22" t="n"/>
       <c r="U3" s="22" t="n"/>
+      <c r="V3" s="22" t="n"/>
+      <c r="W3" s="22" t="n"/>
+      <c r="X3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
@@ -2335,21 +3000,36 @@
           <t>Cost</t>
         </is>
       </c>
+      <c r="V4" s="23" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="W4" s="23" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="X4" s="23" t="inlineStr">
+        <is>
+          <t>Already in BIBS?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-007</t>
+          <t>CR-UA-003</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>Supervisory and record-ownership access</t>
+          <t>Break-glass administrators</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRUM.001.02 (b), FRUM.005.01; Annex Q (C15)</t>
+          <t>FRUM.001.06; Annex N.4, Annex Q.5</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -2359,38 +3039,38 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>BDOI FRS v1.1</t>
+          <t>Best practice (iorta TechNXT)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks that a user with a supervisory role sees and manages the records of the personnel assigned to him or her, with record-ownership rules per role. The system limits each user's data by company and branch (data scope) and by role; it has no supervisor-to-personnel link and no record-owner rule.</t>
+          <t>BDOI's FRS signs every user in through EIAM; two named administrator accounts must still get in when EIAM is down, with each such sign-in alerted to Information Security. The OOTB platform has local accounts only and no break-glass accounts or alert.</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Partly: data scope by company and branch on every user; no supervisor hierarchy or record-owner rule.</t>
+          <t>Not offered: no feature row; the OOTB platform has local accounts with a second factor (UAM-007) but no break-glass accounts kept beside the Enterprise SSO and no sign-in alert.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Supervisor (reports-to) on the user record and in the access requests; data scope "own records", "own and assigned personnel" and "unit" per group profile; the rule applied to the lists, records, documents and reports of every module; audit of the scope changes; screens of the user and the group profile.</t>
+          <t>Two named System Administrator accounts with a local password and second factor while every other user signs in through EIAM; the sign-in method recorded; a notice and e-mail to Information Security at each break-glass sign-in; the setting of the alert addresses.</t>
         </is>
       </c>
       <c r="I5" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="30" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="M5" s="30" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="N5" s="30">
         <f>SUM(I5:M5)</f>
@@ -2406,43 +3086,58 @@
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R5" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="S5" s="12" t="inlineStr">
         <is>
-          <t>BDOI to name the supervisory roles and the record owner of each module (User Access Matrix, Annex C); module FRS of each BRD for the records concerned.</t>
+          <t>Sign-in through EIAM (IS-UA-03, Integration scope).</t>
         </is>
       </c>
       <c r="T5" s="12" t="inlineStr">
         <is>
-          <t>The rule reuses the data scope of the system; the personnel of a supervisor come from the user record (or UIDM-ISC), not from a separate organisation chart.</t>
+          <t>Uses the second factor of the OOTB platform (UAM-007).</t>
         </is>
       </c>
       <c r="U5" s="25">
         <f>IF(DayRate="","",N5*DayRate)</f>
         <v/>
       </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>No feature row (related UAM-007 two-factor authentication: Available)</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>Not found: no break-glass account or break-glass sign-in alert in the OOTB sign-in</t>
+        </is>
+      </c>
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-011</t>
+          <t>CR-UA-007</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Approval times, reminders and escalation</t>
+          <t>Supervisory and record-ownership access</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Annex S (time rules), Annex Q.5, Annex Z</t>
+          <t>FRUM.001.02 (b), FRUM.005.01; Annex Q (C15)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -2452,38 +3147,38 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Best practice (iorta TechNXT)</t>
+          <t>BDOI FRS v1.1</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>The BRD sets no service level for the approval of access requests. Today the age of each request shows on the Access Requests list and report; a reminder and an escalation after a number of working days keep requests from waiting unseen.</t>
+          <t>BDOI's FRS asks that a user with a supervisory role sees and manages the records of the personnel assigned to him or her, with record-ownership rules per role. The OOTB platform limits scoped roles to their own records and clients (UAM-017 Partial); it has no scope by branch or unit, no supervisor-to-personnel link and no record-owner rule per role.</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>No: the age of each request is shown; no reminder or escalation run for access requests.</t>
+          <t>Partial (UAM-017): scoped roles see only their own records and clients. Missing, and estimated here: scope by company, branch and unit, the supervisor link and the record-owner rule per role.</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Settings for the working days per stage, the reminder day and the escalation role; a daily run that sends the reminder notice and escalates overdue requests to the Business Administrator; the overdue marker on the lists; audit of each reminder and escalation.</t>
+          <t>Data scope by company, branch and unit on the user and the group profile; supervisor (reports-to) on the user record and in the access requests; data scope "own records", "own and assigned personnel" and "unit" per group profile; the rule applied to the lists, records, documents and reports of every module; audit of the scope changes; screens of the user and the group profile.</t>
         </is>
       </c>
       <c r="I6" s="30" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" s="30" t="n">
         <v>2</v>
-      </c>
-      <c r="M6" s="30" t="n">
-        <v>1</v>
       </c>
       <c r="N6" s="30">
         <f>SUM(I6:M6)</f>
@@ -2499,84 +3194,99 @@
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="R6" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>Working-day calendar with the public holidays (shared with the out-of-hours rule, Annex Z).</t>
+          <t>BDOI to name the supervisory roles and the record owner of each module (User Access Matrix, Annex C); module FRS of each BRD for the records concerned.</t>
         </is>
       </c>
       <c r="T6" s="12" t="inlineStr">
         <is>
-          <t>Reminders use the notices and e-mails of Annex T; one escalation level.</t>
+          <t>Effort for the missing part only (the own-records scope of the OOTB platform is reused); the personnel of a supervisor come from the user record (or UIDM-ISC), not from a separate organisation chart.</t>
         </is>
       </c>
       <c r="U6" s="25">
         <f>IF(DayRate="","",N6*DayRate)</f>
         <v/>
       </c>
+      <c r="V6" s="12" t="inlineStr">
+        <is>
+          <t>UAM-017 Data-scope restriction: Partial</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>Partial: own-records scope of scoped roles and the reporting line on the user; no branch or unit scope, no supervisor rule</t>
+        </is>
+      </c>
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>Partly (data scope by company and branch; no supervisor link)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-012</t>
+          <t>CR-UA-008</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Monthly access review report to Information Security</t>
+          <t>No conflicting permissions inside a group profile</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Annex V, Annex Q.5 (UA-Q51)</t>
+          <t>FRUM.006.03</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD p.11 lists report volumes only)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Best practice (iorta TechNXT)</t>
+          <t>BDOI FRS v1.1</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Information Security practice is a periodic review of who holds which access. The reports exist and run on demand; producing them each month for Information Security makes the review routine.</t>
+          <t>BDOI's FRS asks that a group profile cannot hold two permissions that conflict. The OOTB platform checks pairs of roles held by one user (separation-of-duties rules); it has no rule on pairs of permissions inside a role.</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Partly: User Access Report and User Access Audit Log run on demand and export; no monthly schedule.</t>
+          <t>Partial: rules on pairs of roles (checked at role assignment). Missing, and estimated here: rules on pairs of permissions, checked when a group profile is changed and when a user is given access.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>A monthly run on the first working day that produces the User Access Report and the audit log of the month, keeps the files for download and notifies Information Security (in the system and by e-mail, with no attachment); run history and failure notice as for the other runs.</t>
+          <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
         </is>
       </c>
       <c r="I7" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K7" s="30" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L7" s="30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="N7" s="30">
         <f>SUM(I7:M7)</f>
@@ -2597,79 +3307,94 @@
       </c>
       <c r="R7" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>UA-Q51 answered (reports, frequency and recipients).</t>
+          <t>BRD items BRD-UA-07 and BRD-UA-09 (rights by function, group profile requests).</t>
         </is>
       </c>
       <c r="T7" s="12" t="inlineStr">
         <is>
-          <t>No new report layout; the files follow the export names of FRUM.007.02.</t>
+          <t>Effort for the permission pairs only; the role-pair rules of the OOTB platform are reused.</t>
         </is>
       </c>
       <c r="U7" s="25">
         <f>IF(DayRate="","",N7*DayRate)</f>
         <v/>
       </c>
+      <c r="V7" s="12" t="inlineStr">
+        <is>
+          <t>UAM-018 Segregation of duties rules: Available (pairs of roles only)</t>
+        </is>
+      </c>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
+        </is>
+      </c>
+      <c r="X7" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-014</t>
+          <t>CR-UA-009</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Temporary access with an end date</t>
+          <t>Export file names</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Annex Z (CLR-UA-06, CLR-UA-13); FRUM.009.10</t>
+          <t>FRUM.007.02; Annex V</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD (BRD NFR 1.k asks for an effective date only)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Best practice (iorta TechNXT)</t>
+          <t>BDOI FRS v1.1</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Access given for a project or a leave cover should end by itself. The system applies changes on an effective date; it has no end date on access.</t>
+          <t>BDOI's FRS names the exports &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY. In the OOTB platform the file names are fixed per report (RPT-009 Not available).</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Partly: effective date and the daily run of scheduled changes; no end date.</t>
+          <t>Not offered: RPT-009 Not available (file names fixed per report).</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>End date on the user requests and the bulk template; validation (after the effective date); the end date on the user's group profiles and in the reports; the daily run removes the access on the end date with a notice a number of days before; audit of each removal.</t>
+          <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
         </is>
       </c>
       <c r="I8" s="30" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="L8" s="30" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N8" s="30">
         <f>SUM(I8:M8)</f>
@@ -2685,7 +3410,7 @@
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="R8" s="12" t="inlineStr">
@@ -2695,92 +3420,542 @@
       </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>Answers to CLR-UA-06 and CLR-UA-13 (Annex Z): who is told and how many days before.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>The removal is a scheduled change of the existing daily run, checked again as the other scheduled changes.</t>
+          <t>The convention of the access reports only; the naming of the other modules' reports is in their own FRS.</t>
         </is>
       </c>
       <c r="U8" s="25">
         <f>IF(DayRate="","",N8*DayRate)</f>
         <v/>
       </c>
+      <c r="V8" s="12" t="inlineStr">
+        <is>
+          <t>RPT-009 Report file naming conventions: Not available</t>
+        </is>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
+        <is>
+          <t>Not found: export file names fixed per report (Reports)</t>
+        </is>
+      </c>
+      <c r="X8" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>CR-UA-011</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Approval times, reminders and escalation</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Annex S (time rules), Annex Q.5, Annex Z</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (iorta TechNXT)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>The BRD sets no service level for the approval of access requests. A reminder and an escalation after a number of working days keep requests from waiting unseen. The OOTB platform has deadlines and escalation for claims, complaints, leads and collections only, and no access requests (WFL-007 Partial).</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Partial (WFL-007): deadlines and escalation exist in other modules, not for access requests. Missing, and estimated here: the time rules, reminder and escalation of access requests.</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Settings for the working days per stage, the reminder day and the escalation role; a daily run that sends the reminder notice and escalates overdue requests to the Business Administrator; the overdue marker on the lists; audit of each reminder and escalation.</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="30">
+        <f>SUM(I9:M9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="30">
+        <f>ROUND(N9*(1-Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="P9" s="30">
+        <f>ROUND(N9*(1+Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>BRD item BRD-UA-08 (access requests); working-day calendar of the OOTB platform (ADM-008).</t>
+        </is>
+      </c>
+      <c r="T9" s="12" t="inlineStr">
+        <is>
+          <t>Reminders use the notices and e-mails of Annex T; one escalation level.</t>
+        </is>
+      </c>
+      <c r="U9" s="25">
+        <f>IF(DayRate="","",N9*DayRate)</f>
+        <v/>
+      </c>
+      <c r="V9" s="12" t="inlineStr">
+        <is>
+          <t>WFL-007 Turnaround-time tracking and escalation: Partial (UAM-019 access requests: Not available)</t>
+        </is>
+      </c>
+      <c r="W9" s="12" t="inlineStr">
+        <is>
+          <t>Not found for access requests: escalation only in the AML and user screens; no access request flow</t>
+        </is>
+      </c>
+      <c r="X9" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>CR-UA-013</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>E-mail copy of the request notices</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.013.01; Annex T</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (iorta TechNXT)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's FRS asks that the notices to approve, returned and decided are also e-mailed, by the user's preference. The OOTB platform sends in-system notices for access-control events (UAM-027 Partial); it has e-mail templates (WFL-011) but no e-mail copy of the access notices.</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Partial (UAM-027): in-system notices only. Missing, and estimated here: the e-mail copy and the user's preference.</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>E-mail copy of the request notices (to approve, returned, decided) from templates, by the user's preference (setting); the outbox status; tests.</t>
+        </is>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N10" s="30">
+        <f>SUM(I10:M10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="30">
+        <f>ROUND(N10*(1-Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="P10" s="30">
+        <f>ROUND(N10*(1+Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" s="12" t="inlineStr">
+        <is>
+          <t>BRD item BRD-UA-14 (notices of the access requests).</t>
+        </is>
+      </c>
+      <c r="T10" s="12" t="inlineStr">
+        <is>
+          <t>Effort for the e-mail copy only; uses the e-mail templates and outbox of the OOTB platform (WFL-011).</t>
+        </is>
+      </c>
+      <c r="U10" s="25">
+        <f>IF(DayRate="","",N10*DayRate)</f>
+        <v/>
+      </c>
+      <c r="V10" s="12" t="inlineStr">
+        <is>
+          <t>UAM-027 Notices of access changes: Partial</t>
+        </is>
+      </c>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>Partial: in-system access-control notices and the e-mail outbox; no e-mail copy of access notices</t>
+        </is>
+      </c>
+      <c r="X10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>CR-UA-014</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Temporary access with an end date</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Annex Z (CLR-UA-06, CLR-UA-13); FRUM.009.10</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD (BRD NFR 1.k asks for an effective date only)</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (iorta TechNXT)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Access given for a project or a leave cover should end by itself. The OOTB platform applies changes at once, with no effective or end date (UAM-024 Not available); the effective date is a BRD requirement (Annex AA.4).</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Not offered: UAM-024 Not available (no effective or end date). The effective date is in scope as BRD item BRD-UA-11; this CR is the end date only.</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>End date on the user requests and the bulk template; validation (after the effective date); the end date on the user's group profiles and in the reports; the daily run removes the access on the end date with a notice a number of days before; audit of each removal.</t>
+        </is>
+      </c>
+      <c r="I11" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L11" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="30">
+        <f>SUM(I11:M11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="30">
+        <f>ROUND(N11*(1-Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="P11" s="30">
+        <f>ROUND(N11*(1+Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R11" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>BRD item BRD-UA-11 (effective dates); answers to CLR-UA-06 and CLR-UA-13 (Annex Z).</t>
+        </is>
+      </c>
+      <c r="T11" s="12" t="inlineStr">
+        <is>
+          <t>The removal is a scheduled change of the daily run of BRD-UA-11, checked again as the other scheduled changes.</t>
+        </is>
+      </c>
+      <c r="U11" s="25">
+        <f>IF(DayRate="","",N11*DayRate)</f>
+        <v/>
+      </c>
+      <c r="V11" s="12" t="inlineStr">
+        <is>
+          <t>UAM-024 Effective-dated access changes: Not available</t>
+        </is>
+      </c>
+      <c r="W11" s="12" t="inlineStr">
+        <is>
+          <t>Not found: no effective or end date on role assignment</t>
+        </is>
+      </c>
+      <c r="X11" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>CR-UA-016</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>Emergency role edit</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.005.01; Annex J</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Not in BRD</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (iorta TechNXT)</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>With group profiles changed only by approved requests, an emergency path lets the System Administrator edit users and group profiles directly, when Information Security opens it, with every edit audited and alerted. The OOTB platform has no request flow and no emergency edit; the feature list has no row for it.</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Not offered: no feature row; in the OOTB platform roles are edited directly with no request, so no controlled emergency path exists.</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed as delivered; every edit audited and alerted to Information Security; the marker on the screens.</t>
+        </is>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M12" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="30">
+        <f>SUM(I12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="30">
+        <f>ROUND(N12*(1-Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="P12" s="30">
+        <f>ROUND(N12*(1+Accuracy),1)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>BRD items BRD-UA-09 and BRD-UA-13 (group profile requests, second approval of security settings).</t>
+        </is>
+      </c>
+      <c r="T12" s="12" t="inlineStr">
+        <is>
+          <t>Alerts use the notices and e-mails of Annex T.</t>
+        </is>
+      </c>
+      <c r="U12" s="25">
+        <f>IF(DayRate="","",N12*DayRate)</f>
+        <v/>
+      </c>
+      <c r="V12" s="12" t="inlineStr">
+        <is>
+          <t>No feature row (UAM-022 group profile requests: Not available)</t>
+        </is>
+      </c>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>Not found: roles edited directly, no emergency path</t>
+        </is>
+      </c>
+      <c r="X12" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>4 change requests</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="31">
-        <f>SUM(I5:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="31">
-        <f>SUM(J5:J8)</f>
-        <v/>
-      </c>
-      <c r="K9" s="31">
-        <f>SUM(K5:K8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="31">
-        <f>SUM(L5:L8)</f>
-        <v/>
-      </c>
-      <c r="M9" s="31">
-        <f>SUM(M5:M8)</f>
-        <v/>
-      </c>
-      <c r="N9" s="31">
-        <f>SUM(N5:N8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="31">
-        <f>SUM(O5:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="31">
-        <f>SUM(P5:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="12" t="n"/>
-      <c r="R9" s="12" t="n"/>
-      <c r="S9" s="12" t="n"/>
-      <c r="T9" s="12" t="n"/>
-      <c r="U9" s="28">
-        <f>IF(DayRate="","",SUM(U5:U8))</f>
-        <v/>
-      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>8 change requests</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="31">
+        <f>SUM(I5:I12)</f>
+        <v/>
+      </c>
+      <c r="J13" s="31">
+        <f>SUM(J5:J12)</f>
+        <v/>
+      </c>
+      <c r="K13" s="31">
+        <f>SUM(K5:K12)</f>
+        <v/>
+      </c>
+      <c r="L13" s="31">
+        <f>SUM(L5:L12)</f>
+        <v/>
+      </c>
+      <c r="M13" s="31">
+        <f>SUM(M5:M12)</f>
+        <v/>
+      </c>
+      <c r="N13" s="31">
+        <f>SUM(N5:N12)</f>
+        <v/>
+      </c>
+      <c r="O13" s="31">
+        <f>SUM(O5:O12)</f>
+        <v/>
+      </c>
+      <c r="P13" s="31">
+        <f>SUM(P5:P12)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="12" t="n"/>
+      <c r="R13" s="12" t="n"/>
+      <c r="S13" s="12" t="n"/>
+      <c r="T13" s="12" t="n"/>
+      <c r="U13" s="28">
+        <f>IF(DayRate="","",SUM(U5:U12))</f>
+        <v/>
+      </c>
+      <c r="V13" s="12" t="n"/>
+      <c r="W13" s="12" t="n"/>
+      <c r="X13" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U9"/>
+  <autoFilter ref="A4:X13"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A2:X2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:U509">
+  <conditionalFormatting sqref="A5:X513">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="Q5:Q509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="Q5:Q513" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="R5:R513" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2804,7 +3979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2815,6 +3990,8 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2827,7 +4004,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Points of the FRS v1.4 that no BRD asks for and the standard system offers (green): no cost</t>
+          <t>Points of the FRS v1.4 that no BRD asks for and the iNXT BrokerVerse OOTB platform offers (green): no cost</t>
         </is>
       </c>
     </row>
@@ -2840,6 +4017,8 @@
       <c r="F3" s="22" t="n"/>
       <c r="G3" s="22" t="n"/>
       <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+      <c r="J3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
@@ -2882,6 +4061,16 @@
           <t>Note</t>
         </is>
       </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
@@ -2906,12 +4095,12 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Pairs of group profiles (and of permissions) one user may not hold, kept by the Business Administrator and authorised by Information Security; checked on every request.</t>
+          <t>Pairs of group profiles one user may not hold (block or warn), kept by the Business Administrator; checked on every assignment.</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="G5" s="12" t="n">
@@ -2922,6 +4111,16 @@
           <t>Extends the segregation-of-duties principle of the Operations addendum; was CR-UA-001</t>
         </is>
       </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>UAM-018 Segregation of duties rules: Available</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>Access Control &gt; Separation-of-duties rules (pairs of roles, block or warn, checked at assignment)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
@@ -2946,12 +4145,12 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Users without a sign-in for 90 days deactivated by the daily run, with a notice 7 days before (settings).</t>
+          <t>Users without a sign-in for 90 days deactivated by the daily run (setting Dormant days).</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="G6" s="12" t="n">
@@ -2959,7 +4158,17 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Was CR-UA-002</t>
+          <t>Was CR-UA-002; the notice 7 days before is a detail BDOI confirms</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>UAM-028 Dormant account deactivation: Available</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Daily run Dormant accounts (setting Dormant days, 90)</t>
         </is>
       </c>
     </row>
@@ -2971,12 +4180,12 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Break-glass administrators</t>
+          <t>Second factor of the local accounts</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRUM.001.06; Annex N.4</t>
+          <t>FRUM-004; Annex M.4</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -2986,12 +4195,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Two named System Administrators with a local password and second factor while sign-in is through EIAM; each sign-in alerted to Information Security.</t>
+          <t>Authenticator code at sign-in, compulsory per role, and reset of a lost authenticator by an administrator.</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
@@ -2999,7 +4208,17 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Was CR-UA-003</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>UAM-007 Two-factor authentication: Available</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Sign-in with authenticator code; two-factor per role on the user screen</t>
         </is>
       </c>
     </row>
@@ -3011,12 +4230,12 @@
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Synchronisation with UIDM-ISC and EIAM</t>
+          <t>Business settings without a release</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>FRUM.002.02, FRUM.003.03; Annex N.3</t>
+          <t>Annex M.10</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -3026,12 +4245,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Joiner, mover, leaver and rehire events applied with the UIDM request number; refused events queued and alerted; Synchronise Now per user.</t>
+          <t>Parameters applied at once and audited, so a point where BDOI's FRS and the BRD differ is chosen by a setting without a release.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="G8" s="12" t="n">
@@ -3039,7 +4258,17 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Refines the BRD requirement 'Integration with SSO or LDAP'; was CR-UA-005</t>
+          <t>The options themselves follow the colour of their own point</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>ADM-011 Business parameters without a release: Available</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Settings screen: parameters applied at once and audited</t>
         </is>
       </c>
     </row>
@@ -3051,12 +4280,12 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Revocation on an SSO status change</t>
+          <t>Periodic access review and scheduled reports</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>FRUM.003.02.01; Annex N</t>
+          <t>Annex V, Annex Q.5 (UA-Q51)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -3066,12 +4295,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>A leaver, or an SSO account inactive, locked or disabled, deactivates the user and ends the open sessions.</t>
+          <t>Recertification campaigns over every active user (revoke deactivates the account) and report schedules with recipients, so the monthly access review reaches Information Security.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Offered as standard</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
@@ -3079,336 +4308,26 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Was CR-UA-006</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-06</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>No conflicting permissions in a role</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.006.03</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Rules on permission pairs refuse a group profile, or a user, that would hold both permissions.</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>Was CR-UA-008</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-07</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Export file names</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.007.02; Annex V</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Exports named &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY (setting).</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Was CR-UA-009</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-08</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>E-mail copy of the request notices</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.013.01; Annex T</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>The notices to approve, returned and decided also e-mailed, by the user's preference (setting).</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>Was CR-UA-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-09</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>Second approval of security settings</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.012.02; Annex M</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>A change of a sign-in, password, session or access setting applies only after the approval of Information Security.</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-10</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>Emergency role edit</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.005.01; Annex J</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>A direct edit of users and group profiles by the System Administrator, closed as delivered; when opened by Information Security every edit is audited and alerted.</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-11</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Second factor of the local accounts</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>FRUM-004; Annex M.4</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Authenticator code at every local sign-in, ten single-use recovery codes, reset of a lost authenticator by one administrator and approved by another.</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-12</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>Settings for the points BDOI decides</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Annex M.10</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Each point where BDOI's FRS and the BRD differ is offered both ways, chosen by a setting changed with the approval of Information Security, without a release.</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-13</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>Identity simulator for SIT and UAT</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Annex N</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>EIAM sign-in and UIDM-ISC events simulated in the test environments until BDOI IT connects the real services.</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>Offered as standard</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Was CR-UA-012</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>UAM-030 Periodic access entitlement review: Available; RPT-007 User-scheduled reports: Available</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>Access Control &gt; Access Reviews; Reports &gt; Schedules (recipients, format, timing)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H17"/>
+  <autoFilter ref="A4:J9"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H517">
+  <conditionalFormatting sqref="A5:J509">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3433,7 +4352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3446,6 +4365,9 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3458,7 +4380,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>BRD requirements found in the validation of the FRS v1.4 (Annex X.2, AA.4): in scope, for planning</t>
+          <t>BRD requirements not (fully) in the iNXT BrokerVerse OOTB platform (FRS Annex X.2, AA.4): in-scope delivery work, for planning</t>
         </is>
       </c>
     </row>
@@ -3473,6 +4395,9 @@
       <c r="H3" s="22" t="n"/>
       <c r="I3" s="22" t="n"/>
       <c r="J3" s="22" t="n"/>
+      <c r="K3" s="22" t="n"/>
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
@@ -3525,6 +4450,21 @@
           <t>Cost</t>
         </is>
       </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="inlineStr">
+        <is>
+          <t>Already in BIBS?</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -3570,6 +4510,21 @@
           <t>Not charged</t>
         </is>
       </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>UAM-005: Not available</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>Not found (several sessions per user)</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -3594,7 +4549,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Minimum length 12 for the break-glass (administrator) accounts, 10 for any other local account; as a setting.</t>
+          <t>Minimum length 12 for the accounts with administrator privileges, 8 or more for any other local account; as a setting.</t>
         </is>
       </c>
       <c r="F6" s="30" t="n">
@@ -3615,6 +4570,21 @@
           <t>Not charged</t>
         </is>
       </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>UAM-008: Available (one minimum length only)</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>Password policy: one minimum length</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -3624,12 +4594,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Idle time-out per the BDO standard</t>
+          <t>Inactivity warning at 15 minutes</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Collections addendum NFR 10.01; UAM BRD x.001.1.2, x.001.1.3</t>
+          <t>UAM BRD x.001.1.2, x.001.1.3; Collections addendum NFR 10.01</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -3639,17 +4609,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Configuration only: the inactivity warning and sign-out times are settings; BDOI confirms 15 or 30 minutes.</t>
+          <t>A warning after 15 minutes of inactivity with Stay Logged In and Log Out, besides the sign-out after 30 minutes; both times settings (BDOI confirms 15 or 30 minutes).</t>
         </is>
       </c>
       <c r="F7" s="30" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I7" s="30">
         <f>SUM(F7:H7)</f>
@@ -3660,13 +4630,748 @@
           <t>Not charged</t>
         </is>
       </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>UAM-003: Partial</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>Partial: idle sign-out with one-minute warning</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-05</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Windows ID, business unit group, user level and user ID rule on the user record</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 13, 15; Collections addendum NFR 2.09</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.002.03; Annex M</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>The fields of the BRD on the user record, screens and reports; the user ID pattern as a setting.</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="30">
+        <f>SUM(F8:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>UAM-012: Partial</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>Partial: users table without Windows ID, BU group, user level</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-07</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Add, amend, delete and task-level rights per group profile</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 4.002.2 to 4.002.2.10; report sample B</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.006; Annex C</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Rights by function (view, add, amend, delete, approve and the tasks of the BRD) per module and group profile, in the screens, the checks and the Group Profile Access Report.</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I9" s="30">
+        <f>SUM(F9:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>UAM-015: Partial</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>Partial: read / write / approve per module</t>
+        </is>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-08</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Access request lifecycle with approval and automatic provisioning</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 1.002 to 1.008, 2.002 (approver chosen by the requester; approve, reject or return)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.002, FRUM.003, FRUM.009, FRUM.010</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Requests to enrol, modify, deactivate and reactivate with draft, cancel and submit; the approver chosen by the requester; approve, reject or return with remarks; the access applied on approval; request history and lists.</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" s="30">
+        <f>SUM(F10:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="inlineStr">
+        <is>
+          <t>UAM-019, UAM-020, UAM-021: Not available</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>Not found (no access requests)</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-09</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Group profile requests approved in sequence and implemented</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 3.002.1 to 3.002.4</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.005, FRUM.011</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Requests to create or change a group profile approved by the approvers in order and implemented by the System Administrator.</t>
+        </is>
+      </c>
+      <c r="F11" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="30">
+        <f>SUM(F11:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>UAM-022: Not available</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>Not found (roles edited directly)</t>
+        </is>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-10</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Bulk access requests with approval</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 1.009; NFR 38</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.002.04; Annex M</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>The bulk template raised as a request, checked row by row with an error file and decided by the approver as a whole (the bulk load of the OOTB platform is reused).</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="30">
+        <f>SUM(F12:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
+        <is>
+          <t>UAM-023: Partial</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>Partial: bulk user load by the System Administrator</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-11</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Effective-dated access changes</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 14 (1.k)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.009.10; Annex Z</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>An effective date on the requests; a daily run applies the scheduled changes, checked again on the day.</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I13" s="30">
+        <f>SUM(F13:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>UAM-024: Not available</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-12</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Escalation of privileged or out-of-hours changes</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 40 (Other BU NFR 11)</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.010.02; Annex S</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Privilege level on the group profiles and the working-hours rule; a second approval of the privileged or out-of-hours changes.</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" s="30">
+        <f>SUM(F14:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="inlineStr">
+        <is>
+          <t>UAM-025: Not available</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-13</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Second approval of security settings</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 16, NFR 40</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.012.02; Annex M</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>A change of a sign-in, password, session or access setting applies only after the approval of Information Security (in the OOTB platform these settings apply at once).</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="30">
+        <f>SUM(F15:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>UAM-026: Partial</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>Partial: settings apply at once (audited)</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-14</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Notices of the access requests to the requester and the user</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 1.006.1.1, 1.008.1.4, 2.002.1; NFR 39</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.013; Annex T</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>In-system notices of each request step (to approve, returned, decided, implemented) to the requester, the approver and the affected user.</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H16" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" s="30">
+        <f>SUM(F16:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>UAM-027: Partial</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>Partial: in-app access-control notices</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-15</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Access reports in the BDOI layout</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 3.003, 4.003.1; samples A to D; NFR 10, NFR 41</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.007; Annex V</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>User Access Report with an 'as of' date, group profile membership, Group Profile Access Report and the from / to User Access Audit Log in the BDOI layout with the header of the BRD.</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I17" s="30">
+        <f>SUM(F17:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>UAM-029: Partial</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>Partial: user access matrix and role permission matrix</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-16</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>On-line status of the users</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 15 (status online), NFR 35</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.001.05; Annex V</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>The list of the users signed in (on-line status) with their sessions; end of a session by the System Administrator.</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I18" s="30">
+        <f>SUM(F18:H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>UAM-004: Partial</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>Partial: end all sessions of a user; no on-line list</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-17</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Access from BDO devices only</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD 1.001.1, 2.001.1, 3.001.1, 4.001.1</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.001.01; Technical Specification</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Access limited to BDO's network and devices: network zone and IP rules of the OOTB platform, plus the device check BDOI IT chooses.</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I19" s="30">
+        <f>SUM(F19:H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>UAM-033: Partial</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>Partial: network / IP rules outside the application</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>Partly (network and IP rules)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J7"/>
+  <autoFilter ref="A4:M19"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J507">
+  <conditionalFormatting sqref="A5:M519">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3691,25 +5396,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
+          <t>Covered by the Integration and Data Migration scope (grey label in the FRS, Annex AA.5): no change request, no cost here</t>
         </is>
       </c>
     </row>
@@ -3717,138 +5427,312 @@
       <c r="A3" s="22" t="n"/>
       <c r="B3" s="22" t="n"/>
       <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Workstream</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Man-day</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>8</v>
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Synchronisation with UIDM-ISC and EIAM (joiner, mover, leaver, rehire; Synchronise Now)</t>
+        </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Hours of work in one man-day</t>
+          <t>FRUM.002.02, FRUM.003.03; Annex N.3</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Events approved in UIDM-ISC applied with the UIDM request number; refused events queued and alerted.</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>UAM-011: Not available</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Was CR-UA-005</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Accuracy of the estimates</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="n">
-        <v>0.2</v>
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-02</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Revocation on an SSO status change</t>
+        </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Plus or minus; the Low and High columns use it</t>
+          <t>FRUM.003.02.01; Annex N</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>A leaver, or an SSO account inactive, locked or disabled, deactivates the user and ends the open sessions.</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>UAM-011: Not available</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Was CR-UA-006</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Day rate</t>
-        </is>
-      </c>
-      <c r="B7" s="34" t="n"/>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Sign-in through Microsoft Entra ID / EIAM with the Windows ID</t>
+        </is>
+      </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Enter the rate of one man-day (currency below); the costs are computed from it</t>
+          <t>FRUM.001.02; Annex N</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Single sign-on of every user (BRD UAM-NFR 11, 17, 33; CLXN NFR 1.01): a BRD requirement delivered by the Integration workstream.</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>UAM-011: Not available</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Was BRD item to deliver</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr"/>
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-04</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>External access-control list interface</t>
+        </is>
+      </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>For example PHP</t>
+          <t>Annex W</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Interface with the access-control list of the system BDOI names (BRD UAM-NFR 12; UQ14).</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>UAM-013: Not available</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr"/>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-05</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>EIAM and UIDM-ISC simulator for SIT and UAT</t>
+        </is>
+      </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Sized on the work needed in the standard iNXT BrokerVerse system as it stands on 11-Oct-2026: a point the system already offers is not a change request (sheet Beyond the BRD - OOTB).</t>
+          <t>Annex N</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Sign-in and identity events simulated in the test environments until BDOI IT connects the real services.</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>No feature row</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr"/>
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>DM-UA-01</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Users and group profiles at go-live</t>
+        </is>
+      </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Analysis and design (FRS update, rules), backend, frontend (screens), testing (test cases of the RTM, regression of the access functions), documentation and UAT support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Not included</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Work of BDOI and BDOI IT (decisions, identity systems, infrastructure), data migration, training beyond the UAT support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Until the sign-off of the FRS v1.4; re-estimated when the decision of BDOI changes the scope of a change request.</t>
+          <t>Annex W (BRD-13 Data Migration)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Users and their group profiles loaded before go-live and at the dress rehearsal (users are not migrated from the legacy systems; loaded by bulk request).</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration (BRD-13)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>MIG-014 Users migration: Available</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C12"/>
+  <autoFilter ref="A4:H10"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:C512">
+  <conditionalFormatting sqref="A5:H510">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3873,62 +5757,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Complexity</t>
-        </is>
-      </c>
-      <c r="B1" s="35" t="inlineStr">
-        <is>
-          <t>Priority</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Insurance-broking best practices in no BRD, not in the FRS and not in OOTB (blue, FRS Annex AA.6): recommendations, not commitments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-01</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Monitoring of privileged sessions</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>System Administrator and break-glass sessions logged in detail (screens opened, data exported) and reviewed by Information Security; expected by the IC and by the BDO group's IT risk rules for privileged access to client and policy data.</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-02</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Alert on unusual sign-in</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Sign-in at an unusual hour, from a new device or network, or many failures across users raised to Information Security; early sign of account takeover of client personal data (Data Privacy Act, NPC breach rules).</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-03</t>
+        </is>
+      </c>
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Log of views of sensitive records</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Who viewed (not only changed) the records of PEP, high-risk and claims clients; supports AMLA confidentiality and Data Privacy Act accountability.</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-04</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Joiner-mover-leaver timeliness report</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Time from the UIDM-ISC approval to access given or removed, and leavers still active; evidence for internal audit that leavers lose access the same day.</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-05</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Separation-of-duties what-if check</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Before a request is submitted the requester sees which separation-of-duties rules the new access would break, so conflicts are fixed before approval.</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B3" s="36" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="E9" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>BP-UA-06</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Generic and shared account register</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Every non-personal account (service, interface, training) with an owner, purpose and review date; a common audit finding in Philippine financial institutions.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
+      <c r="E10" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>6 recommendations (indicative, excluded from the CR total)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12">
+        <f>SUM(E5:E10)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E511">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D511" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Suggested priority" error="Choose a value from the list (Suggested priority)." type="list">
+      <formula1>'Lists'!$B$2:$B$4</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Man-day</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Hours of work in one man-day</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Accuracy of the estimates</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Plus or minus; the Low and High columns use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Day rate</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Enter the rate of one man-day (currency below); the costs are computed from it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>For example PHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Already in BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Activities</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Analysis and design (FRS update, rules), backend, frontend (screens), testing (test cases of the RTM, regression of the access functions), documentation and UAT support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Not included</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Work of BDOI and BDOI IT (decisions, identity systems, infrastructure), data migration, training beyond the UAT support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Until the sign-off of the FRS v1.4; re-estimated when the decision of BDOI changes the scope of a change request.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:C512">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Already in BIBS?</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>Already in BIBS?</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="X4" s="23" t="inlineStr">
         <is>
-          <t>Already in BIBS?</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="M4" s="23" t="inlineStr">
         <is>
-          <t>Already in BIBS?</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       <c r="B9" s="12" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Already in BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
+          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Prepared for BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -23,13 +23,13 @@
     <definedName name="Accuracy">Assumptions!$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$73</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$J$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD items to deliver'!$A$4:$M$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD items to deliver'!$A$4:$M$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD items to deliver'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; Data Migration'!$4:$4</definedName>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -2388,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2512,7 +2512,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-008 No conflicting permissions inside a group profile</t>
+          <t>CR-UA-011 Approval times and reminders of access requests</t>
         </is>
       </c>
       <c r="B7" s="24">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Medium priority; Low complexity</t>
+          <t>Medium priority; Medium complexity</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-009 Export file names</t>
+          <t>CR-UA-014 End date captured on the granting request (temporary access)</t>
         </is>
       </c>
       <c r="B8" s="24">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Low priority; Low complexity</t>
+          <t>Low priority; Medium complexity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-011 Approval times, reminders and escalation</t>
+          <t>CR-UA-016 Emergency role edit</t>
         </is>
       </c>
       <c r="B9" s="24">
@@ -2594,213 +2594,129 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>CR-UA-013 E-mail copy of the request notices</t>
-        </is>
-      </c>
-      <c r="B10" s="24">
-        <f>'CR Effort'!N10</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>'CR Effort'!O10</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>'CR Effort'!P10</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>'CR Effort'!U10</f>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Total of the 5 change requests</t>
+        </is>
+      </c>
+      <c r="B10" s="27">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="27">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>IF(DayRate="","",SUM(E5:E9))</f>
         <v/>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Medium priority; Low complexity</t>
+          <t>Cost appears when the day rate is entered on the sheet Assumptions</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-014 Temporary access with an end date</t>
-        </is>
-      </c>
-      <c r="B11" s="24">
-        <f>'CR Effort'!N11</f>
-        <v/>
-      </c>
-      <c r="C11" s="24">
-        <f>'CR Effort'!O11</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>'CR Effort'!P11</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>'CR Effort'!U11</f>
-        <v/>
+          <t>Points beyond the BRD offered by iNXT BrokerVerse OOTB (5)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Low priority; Medium complexity</t>
+          <t>No change request, no cost (sheet Beyond the BRD - OOTB)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>CR-UA-016 Emergency role edit</t>
+          <t>BRD requirements to deliver (20, in scope)</t>
         </is>
       </c>
       <c r="B12" s="24">
-        <f>'CR Effort'!N12</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>'CR Effort'!O12</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>'CR Effort'!P12</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>'CR Effort'!U12</f>
-        <v/>
+        <f>SUM('BRD items to deliver'!I5:I24)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr"/>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Medium priority; Medium complexity</t>
+          <t>For planning only (FRS Annex AA.4)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>Total of the 8 change requests</t>
-        </is>
-      </c>
-      <c r="B13" s="27">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="27">
-        <f>SUM(C5:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="27">
-        <f>SUM(D5:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>IF(DayRate="","",SUM(E5:E12))</f>
-        <v/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Integration and Data Migration scope (6)</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr"/>
+      <c r="C13" s="24" t="inlineStr"/>
+      <c r="D13" s="24" t="inlineStr"/>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Not here</t>
+        </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Cost appears when the day rate is entered on the sheet Assumptions</t>
+          <t>Covered by the Integration and Data Migration workstreams (FRS Annex AA.5)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Points beyond the BRD offered by iNXT BrokerVerse OOTB (5)</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>0</v>
+          <t>Best-practice recommendations (6, blue)</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>SUM('Best practice (blue)'!E5:E10)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24" t="inlineStr"/>
+      <c r="D14" s="24" t="inlineStr"/>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Indicative</t>
+        </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>No change request, no cost (sheet Beyond the BRD - OOTB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>BRD requirements to deliver (15, in scope)</t>
-        </is>
-      </c>
-      <c r="B15" s="24">
-        <f>SUM('BRD items to deliver'!I5:I19)</f>
-        <v/>
-      </c>
-      <c r="C15" s="24" t="inlineStr"/>
-      <c r="D15" s="24" t="inlineStr"/>
-      <c r="E15" s="25" t="inlineStr">
-        <is>
-          <t>Not charged</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>For planning only (FRS Annex AA.4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Integration and Data Migration scope (6)</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr"/>
-      <c r="C16" s="24" t="inlineStr"/>
-      <c r="D16" s="24" t="inlineStr"/>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>Not here</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>Covered by the Integration and Data Migration workstreams (FRS Annex AA.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Best-practice recommendations (6, blue)</t>
-        </is>
-      </c>
-      <c r="B17" s="24">
-        <f>SUM('Best practice (blue)'!E5:E10)</f>
-        <v/>
-      </c>
-      <c r="C17" s="24" t="inlineStr"/>
-      <c r="D17" s="24" t="inlineStr"/>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>Indicative</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
           <t>Excluded from the CR total (FRS Annex AA.6)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F17"/>
+  <autoFilter ref="A4:F14"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F517">
+  <conditionalFormatting sqref="A5:F514">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2825,7 +2741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3235,42 +3151,42 @@
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-008</t>
+          <t>CR-UA-011</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>No conflicting permissions inside a group profile</t>
+          <t>Approval times and reminders of access requests</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRUM.006.03</t>
+          <t>Annex S (time rules), Annex Q.5, Annex Z</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>Not in BRD (UAM BRD Other BU NFR 11 asks for a configurable, monitored workflow with escalation of risky changes, not for time limits or reminders)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>BDOI FRS v1.1</t>
+          <t>Best practice (iorta TechNXT)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS asks that a group profile cannot hold two permissions that conflict. The OOTB platform checks pairs of roles held by one user (separation-of-duties rules); it has no rule on pairs of permissions inside a role.</t>
+          <t>Only the time-based part is beyond the BRD: a number of working days per approval stage, a reminder to the approver before the limit and the escalation of an overdue request to the Business Administrator. The monitoring of the pending requests (configurable workflow, systematically monitored) is the BRD (NFR 11) and is a BRD item to deliver (BRD-UA-21); the escalation of out-of-hours and low-to-high privilege changes is BRD-UA-12.</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Partial: rules on pairs of roles (checked at role assignment). Missing, and estimated here: rules on pairs of permissions, checked when a group profile is changed and when a user is given access.</t>
+          <t>Partial (WFL-007): deadlines and escalation exist in other modules, not for access requests. Missing, and estimated here: the working days per stage, the reminder and the escalation of an overdue access request.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
+          <t>Settings for the working days per stage, the reminder day and the escalation role; a daily run that sends the reminder notice and escalates overdue requests to the Business Administrator; audit of each reminder and escalation.</t>
         </is>
       </c>
       <c r="I7" s="30" t="n">
@@ -3280,13 +3196,13 @@
         <v>2</v>
       </c>
       <c r="K7" s="30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="30" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M7" s="30" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="N7" s="30">
         <f>SUM(I7:M7)</f>
@@ -3302,7 +3218,7 @@
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="R7" s="12" t="inlineStr">
@@ -3312,12 +3228,12 @@
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>BRD items BRD-UA-07 and BRD-UA-09 (rights by function, group profile requests).</t>
+          <t>BRD items BRD-UA-08 (access requests) and BRD-UA-21 (monitoring of pending requests); working-day calendar of the OOTB platform (ADM-008).</t>
         </is>
       </c>
       <c r="T7" s="12" t="inlineStr">
         <is>
-          <t>Effort for the permission pairs only; the role-pair rules of the OOTB platform are reused.</t>
+          <t>Reminders use the notices and e-mails of Annex T; one escalation level.</t>
         </is>
       </c>
       <c r="U7" s="25">
@@ -3326,75 +3242,75 @@
       </c>
       <c r="V7" s="12" t="inlineStr">
         <is>
-          <t>UAM-018 Segregation of duties rules: Available (pairs of roles only)</t>
+          <t>WFL-007 Turnaround-time tracking and escalation: Partial (UAM-019 access requests: Not available)</t>
         </is>
       </c>
       <c r="W7" s="12" t="inlineStr">
         <is>
-          <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
+          <t>Not found for access requests: escalation only in the AML and user screens; no access request flow</t>
         </is>
       </c>
       <c r="X7" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-009</t>
+          <t>CR-UA-014</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>Export file names</t>
+          <t>End date captured on the granting request (temporary access)</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>FRUM.007.02; Annex V</t>
+          <t>Annex Z (CLR-UA-06, CLR-UA-13); FRUM.009.10</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>Not in BRD (BRD NFR 1.k asks for an effective date of user and role changes; the removal of access on a date is that BRD item)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>BDOI FRS v1.1</t>
+          <t>Best practice (iorta TechNXT)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>BDOI's FRS names the exports &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY. In the OOTB platform the file names are fixed per report (RPT-009 Not available).</t>
+          <t>Only the end date entered with the grant is beyond the BRD: one request that gives access until an end date, with a notice some days before and the end date shown on the user's group profiles and in the reports. A removal of access requested with an effective date is a role change with an effective date (BRD NFR 1.k) and is a BRD item to deliver (BRD-UA-22, on the daily run of BRD-UA-11).</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Not offered: RPT-009 Not available (file names fixed per report).</t>
+          <t>Not offered: UAM-024 Not available (no effective or end date). The effective date and the scheduled removal are in scope (BRD-UA-11, BRD-UA-22); this CR is the end date on the grant only.</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
+          <t>End date on the user requests and the bulk template; validation (after the effective date); the end date on the user's group profiles and in the reports; the notice a number of days before the end date.</t>
         </is>
       </c>
       <c r="I8" s="30" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J8" s="30" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="K8" s="30" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L8" s="30" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="M8" s="30" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="N8" s="30">
         <f>SUM(I8:M8)</f>
@@ -3410,22 +3326,22 @@
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="R8" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BRD items BRD-UA-11 and BRD-UA-22 (effective dates, scheduled removal); answers to CLR-UA-06 and CLR-UA-13 (Annex Z).</t>
         </is>
       </c>
       <c r="T8" s="12" t="inlineStr">
         <is>
-          <t>The convention of the access reports only; the naming of the other modules' reports is in their own FRS.</t>
+          <t>The removal itself runs on the daily run of BRD-UA-11 (BRD-UA-22).</t>
         </is>
       </c>
       <c r="U8" s="25">
@@ -3434,34 +3350,34 @@
       </c>
       <c r="V8" s="12" t="inlineStr">
         <is>
-          <t>RPT-009 Report file naming conventions: Not available</t>
+          <t>UAM-024 Effective-dated access changes: Not available</t>
         </is>
       </c>
       <c r="W8" s="12" t="inlineStr">
         <is>
-          <t>Not found: export file names fixed per report (Reports)</t>
+          <t>Not found: no effective or end date on role assignment</t>
         </is>
       </c>
       <c r="X8" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>CR-UA-011</t>
+          <t>CR-UA-016</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>Approval times, reminders and escalation</t>
+          <t>Emergency role edit</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Annex S (time rules), Annex Q.5, Annex Z</t>
+          <t>FRUM.005.01; Annex J</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -3476,33 +3392,33 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>The BRD sets no service level for the approval of access requests. A reminder and an escalation after a number of working days keep requests from waiting unseen. The OOTB platform has deadlines and escalation for claims, complaints, leads and collections only, and no access requests (WFL-007 Partial).</t>
+          <t>With group profiles changed only by approved requests, an emergency path lets the System Administrator edit users and group profiles directly, when Information Security opens it, with every edit audited and alerted. The OOTB platform has no request flow and no emergency edit; the feature list has no row for it.</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Partial (WFL-007): deadlines and escalation exist in other modules, not for access requests. Missing, and estimated here: the time rules, reminder and escalation of access requests.</t>
+          <t>Not offered: no feature row; in the OOTB platform roles are edited directly with no request, so no controlled emergency path exists.</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Settings for the working days per stage, the reminder day and the escalation role; a daily run that sends the reminder notice and escalates overdue requests to the Business Administrator; the overdue marker on the lists; audit of each reminder and escalation.</t>
+          <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed as delivered; every edit audited and alerted to Information Security; the marker on the screens.</t>
         </is>
       </c>
       <c r="I9" s="30" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="30" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="30" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M9" s="30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="30">
         <f>SUM(I9:M9)</f>
@@ -3528,12 +3444,12 @@
       </c>
       <c r="S9" s="12" t="inlineStr">
         <is>
-          <t>BRD item BRD-UA-08 (access requests); working-day calendar of the OOTB platform (ADM-008).</t>
+          <t>BRD items BRD-UA-09 and BRD-UA-13 (group profile requests, second approval of security settings).</t>
         </is>
       </c>
       <c r="T9" s="12" t="inlineStr">
         <is>
-          <t>Reminders use the notices and e-mails of Annex T; one escalation level.</t>
+          <t>Alerts use the notices and e-mails of Annex T.</t>
         </is>
       </c>
       <c r="U9" s="25">
@@ -3542,420 +3458,96 @@
       </c>
       <c r="V9" s="12" t="inlineStr">
         <is>
-          <t>WFL-007 Turnaround-time tracking and escalation: Partial (UAM-019 access requests: Not available)</t>
+          <t>No feature row (UAM-022 group profile requests: Not available)</t>
         </is>
       </c>
       <c r="W9" s="12" t="inlineStr">
         <is>
-          <t>Not found for access requests: escalation only in the AML and user screens; no access request flow</t>
+          <t>Not found: roles edited directly, no emergency path</t>
         </is>
       </c>
       <c r="X9" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>CR-UA-013</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>E-mail copy of the request notices</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.013.01; Annex T</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Best practice (iorta TechNXT)</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks that the notices to approve, returned and decided are also e-mailed, by the user's preference. The OOTB platform sends in-system notices for access-control events (UAM-027 Partial); it has e-mail templates (WFL-011) but no e-mail copy of the access notices.</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Partial (UAM-027): in-system notices only. Missing, and estimated here: the e-mail copy and the user's preference.</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>E-mail copy of the request notices (to approve, returned, decided) from templates, by the user's preference (setting); the outbox status; tests.</t>
-        </is>
-      </c>
-      <c r="I10" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K10" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L10" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N10" s="30">
-        <f>SUM(I10:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="30">
-        <f>ROUND(N10*(1-Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="P10" s="30">
-        <f>ROUND(N10*(1+Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="R10" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S10" s="12" t="inlineStr">
-        <is>
-          <t>BRD item BRD-UA-14 (notices of the access requests).</t>
-        </is>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>Effort for the e-mail copy only; uses the e-mail templates and outbox of the OOTB platform (WFL-011).</t>
-        </is>
-      </c>
-      <c r="U10" s="25">
-        <f>IF(DayRate="","",N10*DayRate)</f>
-        <v/>
-      </c>
-      <c r="V10" s="12" t="inlineStr">
-        <is>
-          <t>UAM-027 Notices of access changes: Partial</t>
-        </is>
-      </c>
-      <c r="W10" s="12" t="inlineStr">
-        <is>
-          <t>Partial: in-system access-control notices and the e-mail outbox; no e-mail copy of access notices</t>
-        </is>
-      </c>
-      <c r="X10" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>CR-UA-014</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>Temporary access with an end date</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Annex Z (CLR-UA-06, CLR-UA-13); FRUM.009.10</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD (BRD NFR 1.k asks for an effective date only)</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Best practice (iorta TechNXT)</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Access given for a project or a leave cover should end by itself. The OOTB platform applies changes at once, with no effective or end date (UAM-024 Not available); the effective date is a BRD requirement (Annex AA.4).</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Not offered: UAM-024 Not available (no effective or end date). The effective date is in scope as BRD item BRD-UA-11; this CR is the end date only.</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>End date on the user requests and the bulk template; validation (after the effective date); the end date on the user's group profiles and in the reports; the daily run removes the access on the end date with a notice a number of days before; audit of each removal.</t>
-        </is>
-      </c>
-      <c r="I11" s="30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J11" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L11" s="30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M11" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="30">
-        <f>SUM(I11:M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="30">
-        <f>ROUND(N11*(1-Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="P11" s="30">
-        <f>ROUND(N11*(1+Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R11" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S11" s="12" t="inlineStr">
-        <is>
-          <t>BRD item BRD-UA-11 (effective dates); answers to CLR-UA-06 and CLR-UA-13 (Annex Z).</t>
-        </is>
-      </c>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>The removal is a scheduled change of the daily run of BRD-UA-11, checked again as the other scheduled changes.</t>
-        </is>
-      </c>
-      <c r="U11" s="25">
-        <f>IF(DayRate="","",N11*DayRate)</f>
-        <v/>
-      </c>
-      <c r="V11" s="12" t="inlineStr">
-        <is>
-          <t>UAM-024 Effective-dated access changes: Not available</t>
-        </is>
-      </c>
-      <c r="W11" s="12" t="inlineStr">
-        <is>
-          <t>Not found: no effective or end date on role assignment</t>
-        </is>
-      </c>
-      <c r="X11" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>CR-UA-016</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>Emergency role edit</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.005.01; Annex J</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Best practice (iorta TechNXT)</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>With group profiles changed only by approved requests, an emergency path lets the System Administrator edit users and group profiles directly, when Information Security opens it, with every edit audited and alerted. The OOTB platform has no request flow and no emergency edit; the feature list has no row for it.</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>Not offered: no feature row; in the OOTB platform roles are edited directly with no request, so no controlled emergency path exists.</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed as delivered; every edit audited and alerted to Information Security; the marker on the screens.</t>
-        </is>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K12" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M12" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N12" s="30">
-        <f>SUM(I12:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="30">
-        <f>ROUND(N12*(1-Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="P12" s="30">
-        <f>ROUND(N12*(1+Accuracy),1)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R12" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S12" s="12" t="inlineStr">
-        <is>
-          <t>BRD items BRD-UA-09 and BRD-UA-13 (group profile requests, second approval of security settings).</t>
-        </is>
-      </c>
-      <c r="T12" s="12" t="inlineStr">
-        <is>
-          <t>Alerts use the notices and e-mails of Annex T.</t>
-        </is>
-      </c>
-      <c r="U12" s="25">
-        <f>IF(DayRate="","",N12*DayRate)</f>
-        <v/>
-      </c>
-      <c r="V12" s="12" t="inlineStr">
-        <is>
-          <t>No feature row (UAM-022 group profile requests: Not available)</t>
-        </is>
-      </c>
-      <c r="W12" s="12" t="inlineStr">
-        <is>
-          <t>Not found: roles edited directly, no emergency path</t>
-        </is>
-      </c>
-      <c r="X12" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>8 change requests</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="31">
-        <f>SUM(I5:I12)</f>
-        <v/>
-      </c>
-      <c r="J13" s="31">
-        <f>SUM(J5:J12)</f>
-        <v/>
-      </c>
-      <c r="K13" s="31">
-        <f>SUM(K5:K12)</f>
-        <v/>
-      </c>
-      <c r="L13" s="31">
-        <f>SUM(L5:L12)</f>
-        <v/>
-      </c>
-      <c r="M13" s="31">
-        <f>SUM(M5:M12)</f>
-        <v/>
-      </c>
-      <c r="N13" s="31">
-        <f>SUM(N5:N12)</f>
-        <v/>
-      </c>
-      <c r="O13" s="31">
-        <f>SUM(O5:O12)</f>
-        <v/>
-      </c>
-      <c r="P13" s="31">
-        <f>SUM(P5:P12)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="12" t="n"/>
-      <c r="R13" s="12" t="n"/>
-      <c r="S13" s="12" t="n"/>
-      <c r="T13" s="12" t="n"/>
-      <c r="U13" s="28">
-        <f>IF(DayRate="","",SUM(U5:U12))</f>
-        <v/>
-      </c>
-      <c r="V13" s="12" t="n"/>
-      <c r="W13" s="12" t="n"/>
-      <c r="X13" s="12" t="n"/>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>5 change requests</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="31">
+        <f>SUM(I5:I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="31">
+        <f>SUM(J5:J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="31">
+        <f>SUM(K5:K9)</f>
+        <v/>
+      </c>
+      <c r="L10" s="31">
+        <f>SUM(L5:L9)</f>
+        <v/>
+      </c>
+      <c r="M10" s="31">
+        <f>SUM(M5:M9)</f>
+        <v/>
+      </c>
+      <c r="N10" s="31">
+        <f>SUM(N5:N9)</f>
+        <v/>
+      </c>
+      <c r="O10" s="31">
+        <f>SUM(O5:O9)</f>
+        <v/>
+      </c>
+      <c r="P10" s="31">
+        <f>SUM(P5:P9)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="12" t="n"/>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n"/>
+      <c r="T10" s="12" t="n"/>
+      <c r="U10" s="28">
+        <f>IF(DayRate="","",SUM(U5:U9))</f>
+        <v/>
+      </c>
+      <c r="V10" s="12" t="n"/>
+      <c r="W10" s="12" t="n"/>
+      <c r="X10" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X13"/>
+  <autoFilter ref="A4:X10"/>
   <mergeCells count="1">
     <mergeCell ref="A2:X2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:X513">
+  <conditionalFormatting sqref="A5:X510">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="Q5:Q513" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="Q5:Q510" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="R5:R513" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="R5:R510" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4352,7 +3944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5366,12 +4958,312 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-18</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>No conflicting permissions inside a group profile (was CR-UA-008)</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 2.a-2.b (data validation of user and role data, b.1 prevents entry of incorrect data); Other BU NFR 2-3 (define roles and assign permission; permission management)</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.006.03</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I20" s="30">
+        <f>SUM(F20:H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>UAM-018: Available (pairs of roles only)</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-19</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Export file names &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY (was CR-UA-009)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 1.g (report can be exported); Other BU NFR 6 (audit log reports); report samples A to D</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.007.02; Annex V</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G21" s="30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I21" s="30">
+        <f>SUM(F21:H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>RPT-009: Not available</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>Not found: export file names fixed per report (Reports)</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-20</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>E-mail copy of the request notices (was CR-UA-013)</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD Other BU NFR 10 (notification for access changes); BRD 1.006.1.1, 1.008.1.4, 2.002.1</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.013.01; Annex T</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>E-mail copy of the request notices (to approve, returned, decided) from templates, by the user's preference (setting); the outbox status; tests.</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I22" s="30">
+        <f>SUM(F22:H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>UAM-027: Partial</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>Partial: in-system access-control notices and the e-mail outbox; no e-mail copy of access notices</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-21</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Monitoring of the pending access requests (BRD part of CR-UA-011)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD Other BU NFR 11 (configurable workflow for access requests and approvals; changes systematically monitored)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Annex S, Annex Z</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>The age of each pending request and its stage on the request lists, with the overdue marker and the filter of pending requests by approver.</t>
+        </is>
+      </c>
+      <c r="F23" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I23" s="30">
+        <f>SUM(F23:H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>WFL-007: Partial</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>Not found for access requests</t>
+        </is>
+      </c>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>BRD-UA-22</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Scheduled removal of access on its effective date (BRD part of CR-UA-014)</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD NFR 1.k (effective date for user and role changes)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.009.10; Annex Z</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>A request to remove a group profile with an effective date; the daily run of BRD-UA-11 removes the access on that date, with audit of each removal.</t>
+        </is>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I24" s="30">
+        <f>SUM(F24:H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Not charged</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>UAM-024: Not available</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>Not found: no effective or end date on role assignment</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M19"/>
+  <autoFilter ref="A4:M24"/>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:M519">
+  <conditionalFormatting sqref="A5:M524">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -12,32 +12,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; Data Migration" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD covered - OOTB" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; Data Migration" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$7</definedName>
     <definedName name="Accuracy">Assumptions!$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$J$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD items to deliver'!$A$4:$M$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; Data Migration'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Best practice (blue)'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Assumptions'!$A$4:$C$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Assumptions'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$I$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BRD items to deliver'!$A$4:$M$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Integration &amp; Data Migration'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Best practice (blue)'!$A$4:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Assumptions'!$A$4:$C$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Assumptions'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +428,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -738,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E37"/>
+  <dimension ref="B4:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -904,7 +907,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -934,138 +937,153 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements not (fully) in the iNXT BrokerVerse OOTB platform (FRS Annex X.2, AA.4): in-scope delivery work, for planning</t>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform offers: no change request, no effort (FRS Annex AA.4)</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Covered by the Integration and Data Migration scope (grey label in the FRS, Annex AA.5): no change request, no cost here</t>
+          <t>BRD requirements not (fully) in the iNXT BrokerVerse OOTB platform (FRS Annex X.2, AA.4): in-scope delivery work, for planning</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Insurance-broking best practices in no BRD, not in the FRS and not in OOTB (blue, FRS Annex AA.6): recommendations, not commitments</t>
+          <t>Covered by the Integration and Data Migration scope (grey label in the FRS, Annex AA.5): no change request, no cost here</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Insurance-broking best practices in no BRD, not in the FRS and not in OOTB (blue, FRS Annex AA.6): recommendations, not commitments</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="12" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Change request</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>In no BRD and not (or only partly) in the iNXT BrokerVerse OOTB platform (orange in the FRS); also when already available in BIBS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Offered by OOTB</t>
+          <t>Change request</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Not in the BRD; offered by the iNXT BrokerVerse OOTB platform (brokerverse-platform), no cost (green in the FRS)</t>
+          <t>In no BRD and not (or only partly) in the iNXT BrokerVerse OOTB platform (orange in the FRS); also when already available in BIBS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Integration / Data Migration scope</t>
+          <t>Offered by OOTB</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Interfaces and data migration: covered by those workstreams, not a change request (grey label)</t>
+          <t>Not in the BRD; offered by the iNXT BrokerVerse OOTB platform (brokerverse-platform), no cost (green in the FRS)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Best practice</t>
+          <t>Integration / Data Migration scope</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>In no BRD, FRS or OOTB: recommendation with indicative effort, excluded from the CR total (blue)</t>
+          <t>Interfaces and data migration: covered by those workstreams, not a change request (grey label)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="15" t="inlineStr">
         <is>
+          <t>Best practice</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>In no BRD, FRS or OOTB: recommendation with indicative effort, excluded from the CR total (blue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
           <t>BRD requirement</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>In scope; delivered without a change request (black in the FRS)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
+    <row r="38" ht="26" customHeight="1">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -1081,6 +1099,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -1093,11 +1112,193 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Man-day</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Hours of work in one man-day</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Accuracy of the estimates</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Plus or minus; the Low and High columns use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Day rate</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Enter the rate of one man-day (currency below); the costs are computed from it</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>For example PHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Prepared for BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Activities</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Analysis and design (FRS update, rules), backend, frontend (screens), testing (test cases of the RTM, regression of the access functions), documentation and UAT support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Not included</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Work of BDOI and BDOI IT (decisions, identity systems, infrastructure), data migration, training beyond the UAT support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Until the sign-off of the FRS v1.4; re-estimated when the decision of BDOI changes the scope of a change request.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:C512">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1179,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1903,7 +2104,7 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
@@ -1911,18 +2112,22 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Former OB-UA-nn</t>
+        </is>
+      </c>
       <c r="D45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr"/>
@@ -1931,12 +2136,12 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr"/>
@@ -1945,26 +2150,30 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr"/>
+          <t>BRD line</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
+        </is>
+      </c>
       <c r="D48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>What is delivered</t>
+          <t>What BDOI gets</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr"/>
@@ -1973,35 +2182,31 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Analysis and design</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>Man-days</t>
-        </is>
-      </c>
+          <t>OOTB status</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr"/>
       <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>Backend and frontend</t>
+          <t>Effort (man-days)</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Offered by OOTB: no effort</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2009,17 +2214,17 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Testing and UAT support</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2027,17 +2232,17 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Screen or function of the OOTB platform</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr"/>
@@ -2050,14 +2255,10 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="inlineStr">
-        <is>
-          <t>In scope</t>
-        </is>
-      </c>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr"/>
       <c r="D54" s="14" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2068,14 +2269,10 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
-        <is>
-          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
-        </is>
-      </c>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr"/>
       <c r="D55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2086,14 +2283,10 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>brokerverse-platform</t>
-        </is>
-      </c>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr"/>
       <c r="D56" s="14" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2104,132 +2297,148 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
-        </is>
-      </c>
-      <c r="C57" s="12" t="inlineStr">
-        <is>
-          <t>Already available for BDOI in the BIBS system</t>
-        </is>
-      </c>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr"/>
       <c r="D57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>IS-UA-nn / DM-UA-nn</t>
-        </is>
-      </c>
+          <t>What is delivered</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr"/>
       <c r="D58" s="14" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr"/>
+          <t>Analysis and design</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
       <c r="D59" s="12" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr"/>
+          <t>Backend and frontend</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
       <c r="D60" s="14" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="inlineStr"/>
+          <t>Testing and UAT support</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
       <c r="D61" s="12" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Workstream</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr"/>
+          <t>Total man-days</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
       <c r="D62" s="14" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="inlineStr"/>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>In scope</t>
+        </is>
+      </c>
       <c r="D63" s="12" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr"/>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+        </is>
+      </c>
       <c r="D64" s="14" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>No CR cost here</t>
+          <t>brokerverse-platform</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
@@ -2237,17 +2446,17 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>BP-UA-nn</t>
+          <t>Already available for BDOI in the BIBS system</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr"/>
@@ -2255,80 +2464,72 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>Practice</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr"/>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>IS-UA-nn / DM-UA-nn</t>
+        </is>
+      </c>
       <c r="D67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>Philippine market (IC, Data Privacy Act, AMLA) where relevant</t>
-        </is>
-      </c>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr"/>
       <c r="D68" s="14" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr"/>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+      <c r="D69" s="12" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>Not part of the CR total</t>
-        </is>
-      </c>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr"/>
       <c r="D70" s="14" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Workstream</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr"/>
@@ -2337,25 +2538,21 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>Enter the day rate here</t>
-        </is>
-      </c>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr"/>
       <c r="D72" s="14" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
@@ -2366,8 +2563,158 @@
       <c r="C73" s="12" t="inlineStr"/>
       <c r="D73" s="12" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; Data Migration</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>No CR cost here</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>BP-UA-nn</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr"/>
+      <c r="D76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Philippine market (IC, Data Privacy Act, AMLA) where relevant</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr"/>
+      <c r="D78" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Not part of the CR total</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr"/>
+      <c r="D80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Enter the day rate here</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr"/>
+      <c r="D82" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D73"/>
+  <autoFilter ref="A4:D82"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2388,7 +2735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2624,7 +2971,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Points beyond the BRD offered by iNXT BrokerVerse OOTB (5)</t>
+          <t>Points beyond the BRD offered by iNXT BrokerVerse OOTB (4)</t>
         </is>
       </c>
       <c r="B11" s="24" t="n">
@@ -2648,75 +2995,99 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements to deliver (20, in scope)</t>
-        </is>
-      </c>
-      <c r="B12" s="24">
-        <f>SUM('BRD items to deliver'!I5:I24)</f>
-        <v/>
-      </c>
-      <c r="C12" s="24" t="inlineStr"/>
-      <c r="D12" s="24" t="inlineStr"/>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>Not charged</t>
-        </is>
+          <t>BRD requirements offered by iNXT BrokerVerse OOTB (1, in scope)</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>For planning only (FRS Annex AA.4)</t>
+          <t>BRD-covered, no effort (sheet BRD covered - OOTB)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Integration and Data Migration scope (6)</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr"/>
+          <t>BRD requirements to deliver (20, in scope)</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>SUM('BRD items to deliver'!I5:I24)</f>
+        <v/>
+      </c>
       <c r="C13" s="24" t="inlineStr"/>
       <c r="D13" s="24" t="inlineStr"/>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>Not here</t>
+          <t>Not charged</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Covered by the Integration and Data Migration workstreams (FRS Annex AA.5)</t>
+          <t>For planning only (FRS Annex AA.4)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Best-practice recommendations (6, blue)</t>
-        </is>
-      </c>
-      <c r="B14" s="24">
-        <f>SUM('Best practice (blue)'!E5:E10)</f>
-        <v/>
-      </c>
+          <t>Integration and Data Migration scope (6)</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr"/>
       <c r="C14" s="24" t="inlineStr"/>
       <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="25" t="inlineStr">
         <is>
+          <t>Not here</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Covered by the Integration and Data Migration workstreams (FRS Annex AA.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Best-practice recommendations (6, blue)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>SUM('Best practice (blue)'!E5:E10)</f>
+        <v/>
+      </c>
+      <c r="C15" s="24" t="inlineStr"/>
+      <c r="D15" s="24" t="inlineStr"/>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
           <t>Indicative</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Excluded from the CR total (FRS Annex AA.6)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F14"/>
+  <autoFilter ref="A4:F15"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F514">
+  <conditionalFormatting sqref="A5:F515">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3571,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3667,17 +4038,17 @@
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>OB-UA-01</t>
+          <t>OB-UA-02</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Separation-of-duties rules</t>
+          <t>Dormant-user deactivation</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRUM.012.01; Annex M.6</t>
+          <t>FRUM.003.04; Annex V</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -3687,7 +4058,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Pairs of group profiles one user may not hold (block or warn), kept by the Business Administrator; checked on every assignment.</t>
+          <t>Users without a sign-in for 90 days deactivated by the daily run (setting Dormant days).</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -3700,34 +4071,34 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Extends the segregation-of-duties principle of the Operations addendum; was CR-UA-001</t>
+          <t>Was CR-UA-002; the notice 7 days before is a detail BDOI confirms</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>UAM-018 Segregation of duties rules: Available</t>
+          <t>UAM-028 Dormant account deactivation: Available</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>Access Control &gt; Separation-of-duties rules (pairs of roles, block or warn, checked at assignment)</t>
+          <t>Daily run Dormant accounts (setting Dormant days, 90)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>OB-UA-02</t>
+          <t>OB-UA-03</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Dormant-user deactivation</t>
+          <t>Second factor of the local accounts</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>FRUM.003.04; Annex V</t>
+          <t>FRUM-004; Annex M.4</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -3737,7 +4108,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Users without a sign-in for 90 days deactivated by the daily run (setting Dormant days).</t>
+          <t>Authenticator code at sign-in, compulsory per role, and reset of a lost authenticator by an administrator.</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -3750,34 +4121,34 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Was CR-UA-002; the notice 7 days before is a detail BDOI confirms</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>UAM-028 Dormant account deactivation: Available</t>
+          <t>UAM-007 Two-factor authentication: Available</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Daily run Dormant accounts (setting Dormant days, 90)</t>
+          <t>Sign-in with authenticator code; two-factor per role on the user screen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>OB-UA-03</t>
+          <t>OB-UA-04</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Second factor of the local accounts</t>
+          <t>Business settings without a release</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRUM-004; Annex M.4</t>
+          <t>Annex M.10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -3787,7 +4158,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Authenticator code at sign-in, compulsory per role, and reset of a lost authenticator by an administrator.</t>
+          <t>Parameters applied at once and audited, so a point where BDOI's FRS and the BRD differ is chosen by a setting without a release.</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -3800,34 +4171,34 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>The options themselves follow the colour of their own point</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>UAM-007 Two-factor authentication: Available</t>
+          <t>ADM-011 Business parameters without a release: Available</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Sign-in with authenticator code; two-factor per role on the user screen</t>
+          <t>Settings screen: parameters applied at once and audited</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="32" t="inlineStr">
         <is>
-          <t>OB-UA-04</t>
+          <t>OB-UA-05</t>
         </is>
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Business settings without a release</t>
+          <t>Periodic access review and scheduled reports</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Annex M.10</t>
+          <t>Annex V, Annex Q.5 (UA-Q51)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -3837,7 +4208,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Parameters applied at once and audited, so a point where BDOI's FRS and the BRD differ is chosen by a setting without a release.</t>
+          <t>Recertification campaigns over every active user (revoke deactivates the account) and report schedules with recipients, so the monthly access review reaches Information Security.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -3850,76 +4221,26 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>The options themselves follow the colour of their own point</t>
+          <t>Was CR-UA-012</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>ADM-011 Business parameters without a release: Available</t>
+          <t>UAM-030 Periodic access entitlement review: Available; RPT-007 User-scheduled reports: Available</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>Settings screen: parameters applied at once and audited</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t>OB-UA-05</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>Periodic access review and scheduled reports</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Annex V, Annex Q.5 (UA-Q51)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Recertification campaigns over every active user (revoke deactivates the account) and report schedules with recipients, so the monthly access review reaches Information Security.</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Offered by OOTB</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Was CR-UA-012</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>UAM-030 Periodic access entitlement review: Available; RPT-007 User-scheduled reports: Available</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
           <t>Access Control &gt; Access Reviews; Reports &gt; Schedules (recipients, format, timing)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J9"/>
+  <autoFilter ref="A4:J8"/>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J509">
+  <conditionalFormatting sqref="A5:J508">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3939,6 +4260,167 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>BRD covered - OOTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform offers: no change request, no effort (FRS Annex AA.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="22" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="22" t="n"/>
+      <c r="F3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="22" t="n"/>
+      <c r="I3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>BRD line</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>What BDOI gets</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>OOTB status</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Effort (man-days)</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>OB-UA-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Separation-of-duties rules</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.012.01; Annex M.6</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>UAM BRD Other BU NFR 2-3 "Role-Based Access Control - Define roles and assign permission"; "Permission Management"; NFR System Operation 2.b data validation rules (user and role data); Operations addendum "Clear segregation of duties across Marketing, Cashiering, and Disbursement"</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Pairs of group profiles one user may not hold (block or warn), kept by the Business Administrator; checked on every assignment. Was CR-UA-001.</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Offered by OOTB</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>UAM-018 Segregation of duties rules: Available</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Access Control &gt; Separation-of-duties rules (pairs of roles, block or warn, checked at assignment)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:I505">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5282,7 +5764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5643,7 +6125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5902,186 +6384,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Assumptions of the estimate; enter the day rate in the yellow cell</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1">
-      <c r="A3" s="22" t="n"/>
-      <c r="B3" s="22" t="n"/>
-      <c r="C3" s="22" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Man-day</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Hours of work in one man-day</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Accuracy of the estimates</t>
-        </is>
-      </c>
-      <c r="B6" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Plus or minus; the Low and High columns use it</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Day rate</t>
-        </is>
-      </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Enter the rate of one man-day (currency below); the costs are computed from it</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr"/>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>For example PHP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Prepared for BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr"/>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Analysis and design (FRS update, rules), backend, frontend (screens), testing (test cases of the RTM, regression of the access functions), documentation and UAT support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Not included</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Work of BDOI and BDOI IT (decisions, identity systems, infrastructure), data migration, training beyond the UAT support.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr"/>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Until the sign-off of the FRS v1.4; re-estimated when the decision of BDOI changes the scope of a change request.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:C12"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A5:C512">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
-    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -32,9 +32,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BRD items to deliver'!$A$4:$M$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BRD items to deliver'!$A$4:$M$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Integration &amp; Data Migration'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Best practice (blue)'!$A$4:$E$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Best practice (blue)'!$4:$4</definedName>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -3019,11 +3019,11 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements to deliver (20, in scope)</t>
+          <t>BRD requirements to deliver (17, in scope)</t>
         </is>
       </c>
       <c r="B13" s="24">
-        <f>SUM('BRD items to deliver'!I5:I24)</f>
+        <f>SUM('BRD items to deliver'!I5:I21)</f>
         <v/>
       </c>
       <c r="C13" s="24" t="inlineStr"/>
@@ -3042,7 +3042,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Integration and Data Migration scope (6)</t>
+          <t>Integration and Data Migration scope (10)</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr"/>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Only the time-based part is beyond the BRD: a number of working days per approval stage, a reminder to the approver before the limit and the escalation of an overdue request to the Business Administrator. The monitoring of the pending requests (configurable workflow, systematically monitored) is the BRD (NFR 11) and is a BRD item to deliver (BRD-UA-21); the escalation of out-of-hours and low-to-high privilege changes is BRD-UA-12.</t>
+          <t>Only the time-based part is beyond the BRD: a number of working days per approval stage, a reminder to the approver before the limit and the escalation of an overdue request to the Business Administrator. The monitoring of the pending requests (configurable workflow, systematically monitored) is the BRD (NFR 11) and is a BRD item to deliver for the requests that stay in the system (group-profile requests), the monitoring of the user access requests is done in UIDM-ISC (IS-UA-09, BDOI's review comments); the escalation of out-of-hours and low-to-high privilege changes is BRD-UA-12.</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
-          <t>BRD items BRD-UA-08 (access requests) and BRD-UA-21 (monitoring of pending requests); working-day calendar of the OOTB platform (ADM-008).</t>
+          <t>BRD item BRD-UA-09 (group-profile requests); the user access requests in UIDM-ISC (IS-UA-06, IS-UA-08, IS-UA-09); working-day calendar of the OOTB platform (ADM-008).</t>
         </is>
       </c>
       <c r="T7" s="12" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed as delivered; every edit audited and alerted to Information Security; the marker on the screens.</t>
+          <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed by default; every edit audited and alerted to Information Security; the marker on the screens.</t>
         </is>
       </c>
       <c r="I9" s="30" t="n">
@@ -4426,7 +4426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4848,32 +4848,32 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Access request lifecycle with approval and automatic provisioning</t>
+          <t>Access changes received from UIDM-ISC applied in the system (what stays of the request lifecycle)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD 1.002 to 1.008, 2.002 (approver chosen by the requester; approve, reject or return)</t>
+          <t>UAM BRD 1.002 to 1.005 (the change applied), 3.003.1.6 (added / modified / deactivated / reactivated by)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>FRUM.002, FRUM.003, FRUM.009, FRUM.010</t>
+          <t>FRUM.002, FRUM.003, FRUM.009.10; Annex N.3</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Requests to enrol, modify, deactivate and reactivate with draft, cancel and submit; the approver chosen by the requester; approve, reject or return with remarks; the access applied on approval; request history and lists.</t>
+          <t>The access change approved in UIDM-ISC applied to the user's group profiles with the UIDM request number, its history on the user and in the reports, and the notice Your access changed to the user. The raising, correction, cancellation, viewing and approval of the requests are done in UIDM-ISC (IS-UA-06, IS-UA-08; BDOI's review comments): their effort is removed (was 39 man-days).</t>
         </is>
       </c>
       <c r="F10" s="30" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>24</v>
+        <v>2.5</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>11</v>
+        <v>1.25</v>
       </c>
       <c r="I10" s="30">
         <f>SUM(F10:H10)</f>
@@ -4963,37 +4963,37 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-10</t>
+          <t>BRD-UA-11</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Bulk access requests with approval</t>
+          <t>Effective-dated access changes</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD 1.009; NFR 38</t>
+          <t>UAM BRD NFR 14 (1.k)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>FRUM.002.04; Annex M</t>
+          <t>FRUM.009.10; Annex Z</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>The bulk template raised as a request, checked row by row with an error file and decided by the approver as a whole (the bulk load of the OOTB platform is reused).</t>
+          <t>An effective date on the requests; a daily run applies the scheduled changes, checked again on the day.</t>
         </is>
       </c>
       <c r="F12" s="30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G12" s="30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H12" s="30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I12" s="30">
         <f>SUM(F12:H12)</f>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>UAM-023: Partial</t>
+          <t>UAM-024: Not available</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>Partial: bulk user load by the System Administrator</t>
+          <t>Not found</t>
         </is>
       </c>
       <c r="M12" s="12" t="inlineStr">
@@ -5023,34 +5023,34 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-11</t>
+          <t>BRD-UA-12</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Effective-dated access changes</t>
+          <t>Escalation of privileged or out-of-hours changes</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 14 (1.k)</t>
+          <t>UAM BRD NFR 40 (Other BU NFR 11)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>FRUM.009.10; Annex Z</t>
+          <t>FRUM.010.02; Annex S</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>An effective date on the requests; a daily run applies the scheduled changes, checked again on the day.</t>
+          <t>Privilege level on the group profiles and the working-hours rule; a second approval of the privileged or out-of-hours changes made in the system (group-profile requests, security settings); for the user access requests the second approval is given in UIDM-ISC (IS-UA-08).</t>
         </is>
       </c>
       <c r="F13" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="30" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H13" s="30" t="n">
         <v>2.5</v>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>UAM-024: Not available</t>
+          <t>UAM-025: Not available</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -5083,37 +5083,37 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-12</t>
+          <t>BRD-UA-13</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Escalation of privileged or out-of-hours changes</t>
+          <t>Second approval of security settings</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 40 (Other BU NFR 11)</t>
+          <t>UAM BRD NFR 16, NFR 40</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>FRUM.010.02; Annex S</t>
+          <t>FRUM.012.02; Annex M</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Privilege level on the group profiles and the working-hours rule; a second approval of the privileged or out-of-hours changes.</t>
+          <t>A change of a sign-in, password, session or access setting applies only after the approval of Information Security (in the OOTB platform these settings apply at once).</t>
         </is>
       </c>
       <c r="F14" s="30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="30" t="n">
         <v>4</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I14" s="30">
         <f>SUM(F14:H14)</f>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>UAM-025: Not available</t>
+          <t>UAM-026: Partial</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Partial: settings apply at once (audited)</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
@@ -5143,37 +5143,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-13</t>
+          <t>BRD-UA-14</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Second approval of security settings</t>
+          <t>Notices of the group-profile requests and of the access applied</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 16, NFR 40</t>
+          <t>UAM BRD 3.002 (group profile requests); NFR 39 (notification for access changes)</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>FRUM.012.02; Annex M</t>
+          <t>FRUM.013; Annex T</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>A change of a sign-in, password, session or access setting applies only after the approval of Information Security (in the OOTB platform these settings apply at once).</t>
+          <t>In-system notices of the group-profile request steps (to approve, decided, to implement, implemented) and the notice Your access changed to the affected user. The notices of the user access request steps (BRD 1.006.1.1, 1.008.1.4, 2.002.1) are sent by UIDM-ISC (IS-UA-09): their effort is removed (was 4.5 man-days).</t>
         </is>
       </c>
       <c r="F15" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H15" s="30" t="n">
         <v>0.5</v>
-      </c>
-      <c r="G15" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="30" t="n">
-        <v>2</v>
       </c>
       <c r="I15" s="30">
         <f>SUM(F15:H15)</f>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>UAM-026: Partial</t>
+          <t>UAM-027: Partial</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>Partial: settings apply at once (audited)</t>
+          <t>Partial: in-app access-control notices</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
@@ -5203,37 +5203,37 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-14</t>
+          <t>BRD-UA-15</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Notices of the access requests to the requester and the user</t>
+          <t>Access reports in the BDOI layout</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD 1.006.1.1, 1.008.1.4, 2.002.1; NFR 39</t>
+          <t>UAM BRD 3.003, 4.003.1; samples A to D; NFR 10, NFR 41</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>FRUM.013; Annex T</t>
+          <t>FRUM.007; Annex V</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>In-system notices of each request step (to approve, returned, decided, implemented) to the requester, the approver and the affected user.</t>
+          <t>User Access Report with an 'as of' date, group profile membership, Group Profile Access Report and the from / to User Access Audit Log in the BDOI layout with the header of the BRD.</t>
         </is>
       </c>
       <c r="F16" s="30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G16" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="30" t="n">
         <v>2.5</v>
-      </c>
-      <c r="H16" s="30" t="n">
-        <v>1.5</v>
       </c>
       <c r="I16" s="30">
         <f>SUM(F16:H16)</f>
@@ -5246,12 +5246,12 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>UAM-027: Partial</t>
+          <t>UAM-029: Partial</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>Partial: in-app access-control notices</t>
+          <t>Partial: user access matrix and role permission matrix</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
@@ -5263,37 +5263,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-15</t>
+          <t>BRD-UA-16</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Access reports in the BDOI layout</t>
+          <t>On-line status of the users</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD 3.003, 4.003.1; samples A to D; NFR 10, NFR 41</t>
+          <t>UAM BRD NFR 15 (status online), NFR 35</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>FRUM.007; Annex V</t>
+          <t>FRUM.001.05; Annex V</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>User Access Report with an 'as of' date, group profile membership, Group Profile Access Report and the from / to User Access Audit Log in the BDOI layout with the header of the BRD.</t>
+          <t>The list of the users signed in (on-line status) with their sessions; end of a session by the System Administrator.</t>
         </is>
       </c>
       <c r="F17" s="30" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="I17" s="30">
         <f>SUM(F17:H17)</f>
@@ -5306,12 +5306,12 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>UAM-029: Partial</t>
+          <t>UAM-004: Partial</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>Partial: user access matrix and role permission matrix</t>
+          <t>Partial: end all sessions of a user; no on-line list</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
@@ -5323,37 +5323,37 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-16</t>
+          <t>BRD-UA-17</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>On-line status of the users</t>
+          <t>Access from BDO devices only</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 15 (status online), NFR 35</t>
+          <t>UAM BRD 1.001.1, 2.001.1, 3.001.1, 4.001.1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>FRUM.001.05; Annex V</t>
+          <t>FRUM.001.01; Technical Specification</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>The list of the users signed in (on-line status) with their sessions; end of a session by the System Administrator.</t>
+          <t>Access limited to BDO's network and devices: network zone and IP rules of the OOTB platform, plus the device check BDOI IT chooses.</t>
         </is>
       </c>
       <c r="F18" s="30" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="30" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="30">
         <f>SUM(F18:H18)</f>
@@ -5366,54 +5366,54 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>UAM-004: Partial</t>
+          <t>UAM-033: Partial</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>Partial: end all sessions of a user; no on-line list</t>
+          <t>Partial: network / IP rules outside the application</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partly (network and IP rules)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-17</t>
+          <t>BRD-UA-18</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Access from BDO devices only</t>
+          <t>No conflicting permissions inside a group profile (was CR-UA-008)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD 1.001.1, 2.001.1, 3.001.1, 4.001.1</t>
+          <t>UAM BRD NFR 2.a-2.b (data validation of user and role data, b.1 prevents entry of incorrect data); Other BU NFR 2-3 (define roles and assign permission; permission management)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>FRUM.001.01; Technical Specification</t>
+          <t>FRUM.006.03</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Access limited to BDO's network and devices: network zone and IP rules of the OOTB platform, plus the device check BDOI IT chooses.</t>
+          <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
         </is>
       </c>
       <c r="F19" s="30" t="n">
         <v>0.5</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="I19" s="30">
         <f>SUM(F19:H19)</f>
@@ -5426,54 +5426,54 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>UAM-033: Partial</t>
+          <t>UAM-018: Available (pairs of roles only)</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>Partial: network / IP rules outside the application</t>
+          <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>Partly (network and IP rules)</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-18</t>
+          <t>BRD-UA-19</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>No conflicting permissions inside a group profile (was CR-UA-008)</t>
+          <t>Export file names &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY (was CR-UA-009)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 2.a-2.b (data validation of user and role data, b.1 prevents entry of incorrect data); Other BU NFR 2-3 (define roles and assign permission; permission management)</t>
+          <t>UAM BRD NFR 1.g (report can be exported); Other BU NFR 6 (audit log reports); report samples A to D</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>FRUM.006.03</t>
+          <t>FRUM.007.02; Annex V</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
+          <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
         </is>
       </c>
       <c r="F20" s="30" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="I20" s="30">
         <f>SUM(F20:H20)</f>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>UAM-018: Available (pairs of roles only)</t>
+          <t>RPT-009: Not available</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
+          <t>Not found: export file names fixed per report (Reports)</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
@@ -5503,37 +5503,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>BRD-UA-19</t>
+          <t>BRD-UA-22</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Export file names &lt;Report name&gt;_MMDDYYYY and Audit Logs_MMDDYYYY (was CR-UA-009)</t>
+          <t>Scheduled removal of access on its effective date (BRD part of CR-UA-014)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>UAM BRD NFR 1.g (report can be exported); Other BU NFR 6 (audit log reports); report samples A to D</t>
+          <t>UAM BRD NFR 1.k (effective date for user and role changes)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>FRUM.007.02; Annex V</t>
+          <t>FRUM.009.10; Annex Z</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
+          <t>A request to remove a group profile with an effective date; the daily run of BRD-UA-11 removes the access on that date, with audit of each removal.</t>
         </is>
       </c>
       <c r="F21" s="30" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="30" t="n">
         <v>1.25</v>
-      </c>
-      <c r="H21" s="30" t="n">
-        <v>0.75</v>
       </c>
       <c r="I21" s="30">
         <f>SUM(F21:H21)</f>
@@ -5546,206 +5546,26 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>RPT-009: Not available</t>
+          <t>UAM-024: Not available</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>Not found: export file names fixed per report (Reports)</t>
+          <t>Not found: no effective or end date on role assignment</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>BRD-UA-20</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>E-mail copy of the request notices (was CR-UA-013)</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>UAM BRD Other BU NFR 10 (notification for access changes); BRD 1.006.1.1, 1.008.1.4, 2.002.1</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.013.01; Annex T</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>E-mail copy of the request notices (to approve, returned, decided) from templates, by the user's preference (setting); the outbox status; tests.</t>
-        </is>
-      </c>
-      <c r="F22" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I22" s="30">
-        <f>SUM(F22:H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>Not charged</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>UAM-027: Partial</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr">
-        <is>
-          <t>Partial: in-system access-control notices and the e-mail outbox; no e-mail copy of access notices</t>
-        </is>
-      </c>
-      <c r="M22" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>BRD-UA-21</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Monitoring of the pending access requests (BRD part of CR-UA-011)</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>UAM BRD Other BU NFR 11 (configurable workflow for access requests and approvals; changes systematically monitored)</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Annex S, Annex Z</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>The age of each pending request and its stage on the request lists, with the overdue marker and the filter of pending requests by approver.</t>
-        </is>
-      </c>
-      <c r="F23" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H23" s="30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I23" s="30">
-        <f>SUM(F23:H23)</f>
-        <v/>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>Not charged</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
-        <is>
-          <t>WFL-007: Partial</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>Not found for access requests</t>
-        </is>
-      </c>
-      <c r="M23" s="12" t="inlineStr">
-        <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>BRD-UA-22</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled removal of access on its effective date (BRD part of CR-UA-014)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>UAM BRD NFR 1.k (effective date for user and role changes)</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>FRUM.009.10; Annex Z</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>A request to remove a group profile with an effective date; the daily run of BRD-UA-11 removes the access on that date, with audit of each removal.</t>
-        </is>
-      </c>
-      <c r="F24" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I24" s="30">
-        <f>SUM(F24:H24)</f>
-        <v/>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>Not charged</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>UAM-024: Not available</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>Not found: no effective or end date on role assignment</t>
-        </is>
-      </c>
-      <c r="M24" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:M24"/>
+  <autoFilter ref="A4:M21"/>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:M524">
+  <conditionalFormatting sqref="A5:M521">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -5770,7 +5590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6025,17 +5845,17 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>EIAM and UIDM-ISC simulator for SIT and UAT</t>
+          <t>Test accounts and identity events of EIAM and UIDM-ISC in SIT and UAT</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Annex N</t>
+          <t>Annex N.5</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Sign-in and identity events simulated in the test environments until BDOI IT connects the real services.</t>
+          <t>The test accounts and the provisioning events that BDOI IT makes available in the test environments, so that the sign-in and the joiner, mover and leaver flows are tested end to end.</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -6062,51 +5882,219 @@
     <row r="10">
       <c r="A10" s="33" t="inlineStr">
         <is>
+          <t>IS-UA-06</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Access requests raised, corrected, cancelled and viewed in UIDM-ISC</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.009.07, FRUM.009.08, FRUM.009.09; BRD 1.006 to 1.008</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's review comments ("UIDM", Annex Q.6): the requester corrects a returned request, cancels a submitted one and follows the submitted requests in UIDM-ISC; the system receives the approved change through the provisioning interface (IS-UA-01).</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Integration (UIDM-ISC)</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>UAM-019, UAM-021: Not available</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Was BRD-UA-08 (part, 39 man-days with IS-UA-08)</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-07</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Bulk access requests in UIDM-ISC</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.011.01; BRD 1.009</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's review comment ("UIDM", Annex Q.6): bulk creation, modification, deactivation and reactivation are requested and approved in UIDM-ISC and reach the system as provisioning events.</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Integration (UIDM-ISC)</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>UAM-023: Partial</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Was BRD-UA-10 (7.5 man-days)</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-08</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Review, approval, rejection and return of access requests in UIDM-ISC</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.010.01, FRUM.010.02, FRUM.010.03, FRUM.010.04, FRUM.010.05; BRD 2.002</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's review comment ("UIDM", Annex Q.6): the approver receives, lists, approves, rejects and returns the user access requests in UIDM-ISC, with the second approval of privileged changes there; the group-profile requests (BRD 3.002) stay in the system.</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Integration (UIDM-ISC)</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>UAM-020: Not available</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Was BRD-UA-08 (part)</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>IS-UA-09</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Notices, e-mails and monitoring of the user access requests in UIDM-ISC</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>FRUM.013.01; BRD 1.006.1.1, 1.008.1.4, 2.002.1</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>The notices and e-mails of the request steps (to approve, returned, decided) and the monitoring of the pending requests are given by UIDM-ISC with the requests; the system notifies the access applied.</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Integration (UIDM-ISC)</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>UAM-027: Partial; WFL-007: Partial</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Was BRD-UA-14 (part, 3 man-days), BRD-UA-20 (3.75) and BRD-UA-21 (2.75)</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Not a CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
           <t>DM-UA-01</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Users and group profiles at go-live</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Annex W (BRD-13 Data Migration)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Users and their group profiles loaded before go-live and at the dress rehearsal (users are not migrated from the legacy systems; loaded by bulk request).</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Data Migration (BRD-13)</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>MIG-014 Users migration: Available</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Not a CR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H10"/>
+  <autoFilter ref="A4:H14"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H510">
+  <conditionalFormatting sqref="A5:H514">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -22,17 +22,17 @@
   <definedNames>
     <definedName name="DayRate">Assumptions!$B$7</definedName>
     <definedName name="Accuracy">Assumptions!$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$80</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$F$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$W$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$J$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$I$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BRD items to deliver'!$A$4:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'BRD items to deliver'!$A$4:$L$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'BRD items to deliver'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Integration &amp; Data Migration'!$A$4:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Integration &amp; Data Migration'!$4:$4</definedName>
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E38"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -751,13 +751,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -786,6 +789,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -858,6 +862,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1015,6 +1020,7 @@
         <v>8</v>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -1030,7 +1036,7 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>In no BRD and not (or only partly) in the iNXT BrokerVerse OOTB platform (orange in the FRS); also when already available in BIBS</t>
+          <t>In no BRD and not (or only partly) in the iNXT BrokerVerse OOTB platform (orange in the FRS)</t>
         </is>
       </c>
     </row>
@@ -1082,6 +1088,8 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38" ht="26" customHeight="1">
       <c r="B38" s="17" t="inlineStr">
         <is>
@@ -1231,7 +1239,7 @@
       <c r="B9" s="12" t="inlineStr"/>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check), not against the BIBS system configured for BDOI: a point OOTB offers is not a change request; for a partial point only the missing part is estimated; a change request already available in BIBS (column Prepared for BIBS?) keeps its effort as the CR value; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
+          <t>Sized against the iNXT BrokerVerse OOTB platform (repo BDOI-OOTB, branch brokerverse-platform, checked in its code with the Feature List vs OOTB as a cross-check): a point OOTB offers is not a change request; for a partial point only the missing part is estimated; interfaces and data migration are not change requests (sheet Integration &amp; Data Migration); best practice is indicative and excluded (sheet Best practice (blue)) (sheet Beyond the BRD - OOTB).</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1403,6 +1411,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1926,17 +1935,17 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>CR Effort</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Already available for BDOI in the BIBS system; the effort is still the CR value</t>
+          <t>OB-UA-nn</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -1949,14 +1958,10 @@
       </c>
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>OB-UA-nn</t>
-        </is>
-      </c>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr"/>
       <c r="D35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1967,7 +1972,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr"/>
@@ -1981,7 +1986,7 @@
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>BRD reference</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr"/>
@@ -1995,7 +2000,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>What BDOI gets</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr"/>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>What BDOI gets</t>
+          <t>OOTB status</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr"/>
@@ -2023,10 +2028,14 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>OOTB status</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr"/>
+          <t>Cost (man-days)</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>No change request</t>
+        </is>
+      </c>
       <c r="D40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2037,12 +2046,12 @@
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>Cost (man-days)</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>No change request</t>
+          <t>Former change request number, BRD it extends</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2055,12 +2064,12 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Former change request number, BRD it extends</t>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2073,12 +2082,12 @@
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+          <t>Screen or function of the OOTB platform</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2086,17 +2095,17 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Screen or function of the OOTB platform</t>
+          <t>Former OB-UA-nn</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2109,14 +2118,10 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Former OB-UA-nn</t>
-        </is>
-      </c>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr"/>
       <c r="D45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2127,7 +2132,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr"/>
@@ -2141,10 +2146,14 @@
       </c>
       <c r="B47" s="19" t="inlineStr">
         <is>
-          <t>FRS reference</t>
-        </is>
-      </c>
-      <c r="C47" s="12" t="inlineStr"/>
+          <t>BRD line</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
+        </is>
+      </c>
       <c r="D47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2155,14 +2164,10 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>BRD line</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
-        </is>
-      </c>
+          <t>What BDOI gets</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
       <c r="D48" s="14" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2173,7 +2178,7 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>What BDOI gets</t>
+          <t>OOTB status</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr"/>
@@ -2187,10 +2192,14 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>OOTB status</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr"/>
+          <t>Effort (man-days)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Offered by OOTB: no effort</t>
+        </is>
+      </c>
       <c r="D50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2201,12 +2210,12 @@
       </c>
       <c r="B51" s="19" t="inlineStr">
         <is>
-          <t>Effort (man-days)</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Offered by OOTB: no effort</t>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2219,12 +2228,12 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+          <t>Screen or function of the OOTB platform</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr"/>
@@ -2232,19 +2241,15 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>BRD covered - OOTB</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>Screen or function of the OOTB platform</t>
-        </is>
-      </c>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr"/>
       <c r="D53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2255,7 +2260,7 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr"/>
@@ -2269,7 +2274,7 @@
       </c>
       <c r="B55" s="19" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>BRD reference</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr"/>
@@ -2283,7 +2288,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr"/>
@@ -2297,7 +2302,7 @@
       </c>
       <c r="B57" s="19" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>What is delivered</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr"/>
@@ -2311,10 +2316,14 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>What is delivered</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr"/>
+          <t>Analysis and design</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
       <c r="D58" s="14" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2325,7 +2334,7 @@
       </c>
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>Analysis and design</t>
+          <t>Backend and frontend</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
@@ -2343,7 +2352,7 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Backend and frontend</t>
+          <t>Testing and UAT support</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -2361,12 +2370,12 @@
       </c>
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>Testing and UAT support</t>
+          <t>Total man-days</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr"/>
@@ -2379,12 +2388,12 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>Cost</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>In scope</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr"/>
@@ -2397,12 +2406,12 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>In scope</t>
+          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
@@ -2415,12 +2424,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Row of the Feature List vs OOTB workbook (column OOTB platform)</t>
+          <t>brokerverse-platform</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr"/>
@@ -2428,17 +2437,17 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>brokerverse-platform</t>
+          <t>IS-UA-nn / DM-UA-nn</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr"/>
@@ -2446,19 +2455,15 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; Data Migration</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr">
-        <is>
-          <t>Already available for BDOI in the BIBS system</t>
-        </is>
-      </c>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr"/>
       <c r="D66" s="14" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2469,14 +2474,10 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>IS-UA-nn / DM-UA-nn</t>
-        </is>
-      </c>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr"/>
       <c r="D67" s="12" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2487,7 +2488,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr"/>
@@ -2501,7 +2502,7 @@
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>Workstream</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr"/>
@@ -2515,7 +2516,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr"/>
@@ -2529,7 +2530,7 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>Workstream</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr"/>
@@ -2543,42 +2544,46 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr"/>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>No CR cost here</t>
+        </is>
+      </c>
       <c r="D72" s="14" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr"/>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>BP-UA-nn</t>
+        </is>
+      </c>
       <c r="D73" s="12" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; Data Migration</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="C74" s="14" t="inlineStr">
-        <is>
-          <t>No CR cost here</t>
-        </is>
-      </c>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr"/>
       <c r="D74" s="14" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2589,12 +2594,12 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Why it matters for a broker</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>BP-UA-nn</t>
+          <t>Philippine market (IC, Data Privacy Act, AMLA) where relevant</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr"/>
@@ -2607,11 +2612,15 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Suggested priority</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr"/>
-      <c r="D76" s="14" t="inlineStr"/>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -2621,12 +2630,12 @@
       </c>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Indicative man-days</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Philippine market (IC, Data Privacy Act, AMLA) where relevant</t>
+          <t>Not part of the CR total</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr"/>
@@ -2634,35 +2643,31 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>Assumption</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr"/>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+      <c r="D78" s="14" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Not part of the CR total</t>
+          <t>Enter the day rate here</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr"/>
@@ -2675,46 +2680,14 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Assumption</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr"/>
       <c r="D80" s="14" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B81" s="19" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>Enter the day rate here</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B82" s="20" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr"/>
-      <c r="D82" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D82"/>
+  <autoFilter ref="A4:D80"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3112,7 +3085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3138,7 +3111,6 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="40" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3179,7 +3151,6 @@
       <c r="U3" s="22" t="n"/>
       <c r="V3" s="22" t="n"/>
       <c r="W3" s="22" t="n"/>
-      <c r="X3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
@@ -3297,11 +3268,6 @@
           <t>OOTB evidence</t>
         </is>
       </c>
-      <c r="X4" s="23" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS?</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -3405,11 +3371,6 @@
           <t>Not found: no break-glass account or break-glass sign-in alert in the OOTB sign-in</t>
         </is>
       </c>
-      <c r="X5" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -3513,11 +3474,6 @@
           <t>Partial: own-records scope of scoped roles and the reporting line on the user; no branch or unit scope, no supervisor rule</t>
         </is>
       </c>
-      <c r="X6" s="12" t="inlineStr">
-        <is>
-          <t>Partly (data scope by company and branch; no supervisor link)</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -3621,11 +3577,6 @@
           <t>Not found for access requests: escalation only in the AML and user screens; no access request flow</t>
         </is>
       </c>
-      <c r="X7" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -3729,11 +3680,6 @@
           <t>Not found: no effective or end date on role assignment</t>
         </is>
       </c>
-      <c r="X8" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3835,11 +3781,6 @@
       <c r="W9" s="12" t="inlineStr">
         <is>
           <t>Not found: roles edited directly, no emergency path</t>
-        </is>
-      </c>
-      <c r="X9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3902,14 +3843,13 @@
       </c>
       <c r="V10" s="12" t="n"/>
       <c r="W10" s="12" t="n"/>
-      <c r="X10" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:X10"/>
+  <autoFilter ref="A4:W10"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A2:W2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:X510">
+  <conditionalFormatting sqref="A5:W510">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -4426,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4441,7 +4381,6 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4471,7 +4410,6 @@
       <c r="J3" s="22" t="n"/>
       <c r="K3" s="22" t="n"/>
       <c r="L3" s="22" t="n"/>
-      <c r="M3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
@@ -4534,11 +4472,6 @@
           <t>OOTB evidence</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
-        <is>
-          <t>Prepared for BIBS?</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -4594,11 +4527,6 @@
           <t>Not found (several sessions per user)</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -4654,11 +4582,6 @@
           <t>Password policy: one minimum length</t>
         </is>
       </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -4714,11 +4637,6 @@
           <t>Partial: idle sign-out with one-minute warning</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -4774,11 +4692,6 @@
           <t>Partial: users table without Windows ID, BU group, user level</t>
         </is>
       </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -4834,11 +4747,6 @@
           <t>Partial: read / write / approve per module</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -4894,11 +4802,6 @@
           <t>Not found (no access requests)</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -4954,11 +4857,6 @@
           <t>Not found (roles edited directly)</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -5014,11 +4912,6 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -5074,11 +4967,6 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -5134,11 +5022,6 @@
           <t>Partial: settings apply at once (audited)</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -5194,11 +5077,6 @@
           <t>Partial: in-app access-control notices</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -5254,11 +5132,6 @@
           <t>Partial: user access matrix and role permission matrix</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -5314,11 +5187,6 @@
           <t>Partial: end all sessions of a user; no on-line list</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -5374,11 +5242,6 @@
           <t>Partial: network / IP rules outside the application</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
-        <is>
-          <t>Partly (network and IP rules)</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -5434,11 +5297,6 @@
           <t>Partial: Access Control &gt; Separation-of-duties rules on pairs of roles; no rule on pairs of permissions</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -5494,11 +5352,6 @@
           <t>Not found: export file names fixed per report (Reports)</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -5554,18 +5407,13 @@
           <t>Not found: no effective or end date on role assignment</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M21"/>
+  <autoFilter ref="A4:L21"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:M521">
+  <conditionalFormatting sqref="A5:L521">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,7 +270,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -279,19 +279,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1113,7 +1116,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1195,7 +1198,7 @@
           <t>Accuracy of the estimates</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="36" t="n">
         <v>0.2</v>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -1210,7 +1213,7 @@
           <t>Day rate</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n"/>
+      <c r="B7" s="37" t="n"/>
       <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Enter the rate of one man-day (currency below); the costs are computed from it</t>
@@ -1296,7 +1299,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1320,48 +1323,48 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="B1" s="37" t="inlineStr">
+      <c r="B1" s="38" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1372,7 +1375,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2692,7 +2695,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2999,8 +3002,8 @@
         <f>SUM('BRD items to deliver'!I5:I21)</f>
         <v/>
       </c>
-      <c r="C13" s="24" t="inlineStr"/>
-      <c r="D13" s="24" t="inlineStr"/>
+      <c r="C13" s="29" t="inlineStr"/>
+      <c r="D13" s="29" t="inlineStr"/>
       <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Not charged</t>
@@ -3018,9 +3021,9 @@
           <t>Integration and Data Migration scope (10)</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr"/>
-      <c r="C14" s="24" t="inlineStr"/>
-      <c r="D14" s="24" t="inlineStr"/>
+      <c r="B14" s="29" t="inlineStr"/>
+      <c r="C14" s="29" t="inlineStr"/>
+      <c r="D14" s="29" t="inlineStr"/>
       <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Not here</t>
@@ -3042,8 +3045,8 @@
         <f>SUM('Best practice (blue)'!E5:E10)</f>
         <v/>
       </c>
-      <c r="C15" s="24" t="inlineStr"/>
-      <c r="D15" s="24" t="inlineStr"/>
+      <c r="C15" s="29" t="inlineStr"/>
+      <c r="D15" s="29" t="inlineStr"/>
       <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Indicative</t>
@@ -3069,7 +3072,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3270,12 +3273,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>CR-UA-003</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Break-glass administrators</t>
         </is>
@@ -3310,30 +3313,30 @@
           <t>Two named System Administrator accounts with a local password and second factor while every other user signs in through EIAM; the sign-in method recorded; a notice and e-mail to Information Security at each break-glass sign-in; the setting of the alert addresses.</t>
         </is>
       </c>
-      <c r="I5" s="30" t="n">
+      <c r="I5" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="30" t="n">
+      <c r="J5" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="30" t="n">
+      <c r="K5" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="30" t="n">
+      <c r="L5" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="M5" s="30" t="n">
+      <c r="M5" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="N5" s="30">
+      <c r="N5" s="31">
         <f>SUM(I5:M5)</f>
         <v/>
       </c>
-      <c r="O5" s="30">
+      <c r="O5" s="31">
         <f>ROUND(N5*(1-Accuracy),1)</f>
         <v/>
       </c>
-      <c r="P5" s="30">
+      <c r="P5" s="31">
         <f>ROUND(N5*(1+Accuracy),1)</f>
         <v/>
       </c>
@@ -3373,12 +3376,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>CR-UA-007</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Supervisory and record-ownership access</t>
         </is>
@@ -3413,30 +3416,30 @@
           <t>Data scope by company, branch and unit on the user and the group profile; supervisor (reports-to) on the user record and in the access requests; data scope "own records", "own and assigned personnel" and "unit" per group profile; the rule applied to the lists, records, documents and reports of every module; audit of the scope changes; screens of the user and the group profile.</t>
         </is>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="K6" s="30" t="n">
+      <c r="K6" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="L6" s="30" t="n">
+      <c r="L6" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="M6" s="30" t="n">
+      <c r="M6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="30">
+      <c r="N6" s="31">
         <f>SUM(I6:M6)</f>
         <v/>
       </c>
-      <c r="O6" s="30">
+      <c r="O6" s="31">
         <f>ROUND(N6*(1-Accuracy),1)</f>
         <v/>
       </c>
-      <c r="P6" s="30">
+      <c r="P6" s="31">
         <f>ROUND(N6*(1+Accuracy),1)</f>
         <v/>
       </c>
@@ -3476,12 +3479,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>CR-UA-011</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Approval times and reminders of access requests</t>
         </is>
@@ -3516,30 +3519,30 @@
           <t>Settings for the working days per stage, the reminder day and the escalation role; a daily run that sends the reminder notice and escalates overdue requests to the Business Administrator; audit of each reminder and escalation.</t>
         </is>
       </c>
-      <c r="I7" s="30" t="n">
+      <c r="I7" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="J7" s="30" t="n">
+      <c r="J7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="30" t="n">
+      <c r="K7" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="L7" s="30" t="n">
+      <c r="L7" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="M7" s="30" t="n">
+      <c r="M7" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="31">
         <f>SUM(I7:M7)</f>
         <v/>
       </c>
-      <c r="O7" s="30">
+      <c r="O7" s="31">
         <f>ROUND(N7*(1-Accuracy),1)</f>
         <v/>
       </c>
-      <c r="P7" s="30">
+      <c r="P7" s="31">
         <f>ROUND(N7*(1+Accuracy),1)</f>
         <v/>
       </c>
@@ -3579,12 +3582,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>CR-UA-014</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>End date captured on the granting request (temporary access)</t>
         </is>
@@ -3619,30 +3622,30 @@
           <t>End date on the user requests and the bulk template; validation (after the effective date); the end date on the user's group profiles and in the reports; the notice a number of days before the end date.</t>
         </is>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="K8" s="30" t="n">
+      <c r="K8" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="30" t="n">
+      <c r="L8" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="M8" s="30" t="n">
+      <c r="M8" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="31">
         <f>SUM(I8:M8)</f>
         <v/>
       </c>
-      <c r="O8" s="30">
+      <c r="O8" s="31">
         <f>ROUND(N8*(1-Accuracy),1)</f>
         <v/>
       </c>
-      <c r="P8" s="30">
+      <c r="P8" s="31">
         <f>ROUND(N8*(1+Accuracy),1)</f>
         <v/>
       </c>
@@ -3682,12 +3685,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>CR-UA-016</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Emergency role edit</t>
         </is>
@@ -3722,30 +3725,30 @@
           <t>The emergency role edit setting, opened by Information Security; the direct edit of users and group profiles by the System Administrator while it is open, closed by default; every edit audited and alerted to Information Security; the marker on the screens.</t>
         </is>
       </c>
-      <c r="I9" s="30" t="n">
+      <c r="I9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="30" t="n">
+      <c r="J9" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="K9" s="30" t="n">
+      <c r="K9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="30" t="n">
+      <c r="L9" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="M9" s="30" t="n">
+      <c r="M9" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="31">
         <f>SUM(I9:M9)</f>
         <v/>
       </c>
-      <c r="O9" s="30">
+      <c r="O9" s="31">
         <f>ROUND(N9*(1-Accuracy),1)</f>
         <v/>
       </c>
-      <c r="P9" s="30">
+      <c r="P9" s="31">
         <f>ROUND(N9*(1+Accuracy),1)</f>
         <v/>
       </c>
@@ -3801,35 +3804,35 @@
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
-      <c r="I10" s="31">
+      <c r="I10" s="32">
         <f>SUM(I5:I9)</f>
         <v/>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="32">
         <f>SUM(J5:J9)</f>
         <v/>
       </c>
-      <c r="K10" s="31">
+      <c r="K10" s="32">
         <f>SUM(K5:K9)</f>
         <v/>
       </c>
-      <c r="L10" s="31">
+      <c r="L10" s="32">
         <f>SUM(L5:L9)</f>
         <v/>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="32">
         <f>SUM(M5:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="31">
+      <c r="N10" s="32">
         <f>SUM(N5:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="31">
+      <c r="O10" s="32">
         <f>SUM(O5:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="31">
+      <c r="P10" s="32">
         <f>SUM(P5:P9)</f>
         <v/>
       </c>
@@ -3866,7 +3869,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3976,12 +3979,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>OB-UA-02</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Dormant-user deactivation</t>
         </is>
@@ -4006,7 +4009,7 @@
           <t>Offered by OOTB</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -4026,12 +4029,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>OB-UA-03</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Second factor of the local accounts</t>
         </is>
@@ -4056,7 +4059,7 @@
           <t>Offered by OOTB</t>
         </is>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -4076,12 +4079,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>OB-UA-04</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Business settings without a release</t>
         </is>
@@ -4106,7 +4109,7 @@
           <t>Offered by OOTB</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -4126,12 +4129,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>OB-UA-05</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Periodic access review and scheduled reports</t>
         </is>
@@ -4156,7 +4159,7 @@
           <t>Offered by OOTB</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -4189,7 +4192,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4322,7 +4325,7 @@
           <t>Offered by OOTB</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="24" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -4350,7 +4353,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4499,16 +4502,16 @@
           <t>A sign-in on another device ends the user's earlier session, with the reason in the session log and a message on the earlier device.</t>
         </is>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>SUM(F5:H5)</f>
         <v/>
       </c>
@@ -4554,16 +4557,16 @@
           <t>Minimum length 12 for the accounts with administrator privileges, 8 or more for any other local account; as a setting.</t>
         </is>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="31">
         <f>SUM(F6:H6)</f>
         <v/>
       </c>
@@ -4609,16 +4612,16 @@
           <t>A warning after 15 minutes of inactivity with Stay Logged In and Log Out, besides the sign-out after 30 minutes; both times settings (BDOI confirms 15 or 30 minutes).</t>
         </is>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <f>SUM(F7:H7)</f>
         <v/>
       </c>
@@ -4664,16 +4667,16 @@
           <t>The fields of the BRD on the user record, screens and reports; the user ID pattern as a setting.</t>
         </is>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <f>SUM(F8:H8)</f>
         <v/>
       </c>
@@ -4719,16 +4722,16 @@
           <t>Rights by function (view, add, amend, delete, approve and the tasks of the BRD) per module and group profile, in the screens, the checks and the Group Profile Access Report.</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <f>SUM(F9:H9)</f>
         <v/>
       </c>
@@ -4774,16 +4777,16 @@
           <t>The access change approved in UIDM-ISC applied to the user's group profiles with the UIDM request number, its history on the user and in the reports, and the notice Your access changed to the user. The raising, correction, cancellation, viewing and approval of the requests are done in UIDM-ISC (IS-UA-06, IS-UA-08; BDOI's review comments): their effort is removed (was 39 man-days).</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="H10" s="30" t="n">
+      <c r="H10" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="31">
         <f>SUM(F10:H10)</f>
         <v/>
       </c>
@@ -4829,16 +4832,16 @@
           <t>Requests to create or change a group profile approved by the approvers in order and implemented by the System Administrator.</t>
         </is>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="31">
         <f>SUM(F11:H11)</f>
         <v/>
       </c>
@@ -4884,16 +4887,16 @@
           <t>An effective date on the requests; a daily run applies the scheduled changes, checked again on the day.</t>
         </is>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F12" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="31" t="n">
         <v>4.5</v>
       </c>
-      <c r="H12" s="30" t="n">
+      <c r="H12" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="31">
         <f>SUM(F12:H12)</f>
         <v/>
       </c>
@@ -4939,16 +4942,16 @@
           <t>Privilege level on the group profiles and the working-hours rule; a second approval of the privileged or out-of-hours changes made in the system (group-profile requests, security settings); for the user access requests the second approval is given in UIDM-ISC (IS-UA-08).</t>
         </is>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="31">
         <f>SUM(F13:H13)</f>
         <v/>
       </c>
@@ -4994,16 +4997,16 @@
           <t>A change of a sign-in, password, session or access setting applies only after the approval of Information Security (in the OOTB platform these settings apply at once).</t>
         </is>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="31">
         <f>SUM(F14:H14)</f>
         <v/>
       </c>
@@ -5049,16 +5052,16 @@
           <t>In-system notices of the group-profile request steps (to approve, decided, to implement, implemented) and the notice Your access changed to the affected user. The notices of the user access request steps (BRD 1.006.1.1, 1.008.1.4, 2.002.1) are sent by UIDM-ISC (IS-UA-09): their effort is removed (was 4.5 man-days).</t>
         </is>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="31">
         <f>SUM(F15:H15)</f>
         <v/>
       </c>
@@ -5104,16 +5107,16 @@
           <t>User Access Report with an 'as of' date, group profile membership, Group Profile Access Report and the from / to User Access Audit Log in the BDOI layout with the header of the BRD.</t>
         </is>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="31">
         <f>SUM(F16:H16)</f>
         <v/>
       </c>
@@ -5159,16 +5162,16 @@
           <t>The list of the users signed in (on-line status) with their sessions; end of a session by the System Administrator.</t>
         </is>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G17" s="30" t="n">
+      <c r="G17" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="30" t="n">
+      <c r="H17" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="31">
         <f>SUM(F17:H17)</f>
         <v/>
       </c>
@@ -5214,16 +5217,16 @@
           <t>Access limited to BDO's network and devices: network zone and IP rules of the OOTB platform, plus the device check BDOI IT chooses.</t>
         </is>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="H18" s="30" t="n">
+      <c r="H18" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="31">
         <f>SUM(F18:H18)</f>
         <v/>
       </c>
@@ -5269,16 +5272,16 @@
           <t>Rules on pairs of permissions kept by the Business Administrator; check on every group profile change and access request; message naming the conflict; audit.</t>
         </is>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="31">
         <f>SUM(F19:H19)</f>
         <v/>
       </c>
@@ -5324,16 +5327,16 @@
           <t>File names of the User Access reports and of the audit log export by BDOI's convention, as a setting; test of every export.</t>
         </is>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="31" t="n">
         <v>0.25</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="31" t="n">
         <v>0.75</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="31">
         <f>SUM(F20:H20)</f>
         <v/>
       </c>
@@ -5379,16 +5382,16 @@
           <t>A request to remove a group profile with an effective date; the daily run of BRD-UA-11 removes the access on that date, with audit of each removal.</t>
         </is>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="31" t="n">
         <v>1.25</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <f>SUM(F21:H21)</f>
         <v/>
       </c>
@@ -5422,7 +5425,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5518,7 +5521,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>IS-UA-01</t>
         </is>
@@ -5560,7 +5563,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>IS-UA-02</t>
         </is>
@@ -5602,7 +5605,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>IS-UA-03</t>
         </is>
@@ -5644,7 +5647,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>IS-UA-04</t>
         </is>
@@ -5686,7 +5689,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>IS-UA-05</t>
         </is>
@@ -5728,7 +5731,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>IS-UA-06</t>
         </is>
@@ -5770,7 +5773,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>IS-UA-07</t>
         </is>
@@ -5812,7 +5815,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>IS-UA-08</t>
         </is>
@@ -5854,7 +5857,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>IS-UA-09</t>
         </is>
@@ -5896,7 +5899,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>DM-UA-01</t>
         </is>
@@ -5951,7 +5954,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -6026,12 +6029,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>BP-UA-01</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Monitoring of privileged sessions</t>
         </is>
@@ -6046,17 +6049,17 @@
           <t>High</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="24" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>BP-UA-02</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Alert on unusual sign-in</t>
         </is>
@@ -6071,17 +6074,17 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="24" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>BP-UA-03</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Log of views of sensitive records</t>
         </is>
@@ -6096,17 +6099,17 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="24" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>BP-UA-04</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Joiner-mover-leaver timeliness report</t>
         </is>
@@ -6121,17 +6124,17 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="24" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>BP-UA-05</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Separation-of-duties what-if check</t>
         </is>
@@ -6146,17 +6149,17 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="24" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>BP-UA-06</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Generic and shared account register</t>
         </is>
@@ -6171,7 +6174,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="24" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6188,7 +6191,7 @@
       </c>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12">
+      <c r="E11" s="24">
         <f>SUM(E5:E10)</f>
         <v/>
       </c>
@@ -6212,7 +6215,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-11_User_Access_Maintenance/BIBS_CR_BRD-11_Effort_Estimate_v1.0.xlsx
@@ -3867,7 +3867,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
@@ -4190,7 +4190,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
@@ -4351,7 +4351,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
@@ -5423,7 +5423,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8CR Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
